--- a/workspaces/btc_daily_14days/cycle/days_since_halving.xlsx
+++ b/workspaces/btc_daily_14days/cycle/days_since_halving.xlsx
@@ -575,46 +575,46 @@
         <v>141</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.103367398224158</v>
+        <v>-7.079996188559107</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.588920977452553</v>
+        <v>-6.567606947938181</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-10.53358324274757</v>
+        <v>-10.49891348651816</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-16.08398922577403</v>
+        <v>-16.03097496994977</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-15.20715094704936</v>
+        <v>-15.15705453200768</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-19.17378266695395</v>
+        <v>-19.11094381234167</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-17.84308434121971</v>
+        <v>-17.78420200354726</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-17.60508807647417</v>
+        <v>-17.54711428272903</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-16.96037418156242</v>
+        <v>-16.90394973681031</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-15.68421308898581</v>
+        <v>-15.63207437595878</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-13.76060106027307</v>
+        <v>-13.71459373067981</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-15.86324657923475</v>
+        <v>-15.81034915924912</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-13.44324706242956</v>
+        <v>-13.39841368049623</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.503649734982673</v>
+        <v>-7.478382204658971</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>138</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.028300810224806</v>
+        <v>4.015571936500891</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.417320887981589</v>
+        <v>2.409602908609386</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.472729117505452</v>
+        <v>3.462359898108573</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.229720597502386</v>
+        <v>7.207424704338351</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.94645679162518</v>
+        <v>13.90119792954933</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.61976950921748</v>
+        <v>10.58600853680495</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12.71470287098399</v>
+        <v>12.67410165025891</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.52391711856368</v>
+        <v>11.48719332111768</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>11.46529520004017</v>
+        <v>11.42929767983014</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>14.2478524397447</v>
+        <v>14.20214106109525</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.8665165890053</v>
+        <v>11.82884667604776</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>12.63041731913357</v>
+        <v>12.59040479907185</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.75849719463881</v>
+        <v>10.72440838174915</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.104096439102747</v>
+        <v>8.078201205764131</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>141</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.20868933936449</v>
+        <v>9.176731714176555</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.017984311934953</v>
+        <v>8.986409012043303</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.46361677747753</v>
+        <v>11.42428782068201</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12.30670469781406</v>
+        <v>12.26482069846687</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>13.1912178945235</v>
+        <v>13.14519713473726</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>12.07199685112695</v>
+        <v>12.030560731779</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>14.12143199583861</v>
+        <v>14.07279844009658</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>13.65712306840198</v>
+        <v>13.61009885955519</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>16.4423095562415</v>
+        <v>16.38603959372906</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>17.72775179989678</v>
+        <v>17.66631159935248</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>17.52698502854835</v>
+        <v>17.46650632919868</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>17.56598990115972</v>
+        <v>17.50554723825454</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>19.99538173566987</v>
+        <v>19.92614503077348</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>22.38706694829413</v>
+        <v>22.30885183789455</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>141</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.790249623052432</v>
+        <v>7.760950674121958</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.30875760505144</v>
+        <v>8.277271338612003</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.88333842130021</v>
+        <v>12.83567693568723</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15.85657592753756</v>
+        <v>15.79834685943624</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>13.90236606023429</v>
+        <v>13.85007830089519</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>16.3345938371136</v>
+        <v>16.27423534143404</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>16.25448586459499</v>
+        <v>16.19416467122962</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>17.92287671275836</v>
+        <v>17.85647415527291</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>19.99918719553802</v>
+        <v>19.92540241668615</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>21.99729002996223</v>
+        <v>21.91531115667608</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>26.77662763228915</v>
+        <v>26.67742915091311</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>29.66432484843556</v>
+        <v>29.55472167079395</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>32.09815885401644</v>
+        <v>31.97904599195143</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>31.64709346468497</v>
+        <v>31.52870999392292</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>138</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8.376126897181337</v>
+        <v>8.342194494226639</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.491571482819325</v>
+        <v>7.460624756066004</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>6.373797247455904</v>
+        <v>6.347064893525229</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.956796593860069</v>
+        <v>7.923934668170098</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.146078982175943</v>
+        <v>8.111468290665371</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.269306600021977</v>
+        <v>6.242401365430197</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.008872244015748</v>
+        <v>3.990324338243916</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.268402159396459</v>
+        <v>4.248649207443755</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.029794587808041</v>
+        <v>2.018514547982299</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.179151248867583</v>
+        <v>1.169872991340107</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.428358876323685</v>
+        <v>2.413917178258373</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.191156799844869</v>
+        <v>3.173564155675024</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.953300210623766</v>
+        <v>4.927981560368679</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.116517629131636</v>
+        <v>8.078201205763804</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>141</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.82571061596024</v>
+        <v>2.810966542124305</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.14691769886576</v>
+        <v>11.09878283695122</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>11.4651468931131</v>
+        <v>11.41587218468611</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>15.14875392686134</v>
+        <v>15.08446747634814</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11.77461950209204</v>
+        <v>11.72261443969408</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>15.62771369885631</v>
+        <v>15.56127193144039</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>16.25843385301854</v>
+        <v>16.18955868473441</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>17.21719073528937</v>
+        <v>17.14422525652886</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>13.60668549986007</v>
+        <v>13.54837555095289</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>13.4707301911735</v>
+        <v>13.41174909921114</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>12.55899061970608</v>
+        <v>12.50300394263125</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>11.174906043512</v>
+        <v>11.12404217562215</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8.622798552706122</v>
+        <v>8.580716087982744</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.454187908412358</v>
+        <v>7.415234816617954</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>138</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.044162957891139</v>
+        <v>-1.044143605757114</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.4815070318657249</v>
+        <v>-0.4856214735103563</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.749181751363686</v>
+        <v>2.73172548435268</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.7051462634395449</v>
+        <v>0.6951362526618894</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.8925698602907701</v>
+        <v>0.8811391772258546</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2603359624849659</v>
+        <v>-0.2666922736883635</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.522818372898158</v>
+        <v>-2.519804724632145</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.264764617679717</v>
+        <v>-2.2632947972984</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1471422183032445</v>
+        <v>-0.153508643850742</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2716008617549051</v>
+        <v>-0.2787460383990208</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2509080717271175</v>
+        <v>0.2410654631153406</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.168070871276001</v>
+        <v>-1.172188915978779</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.8612354029096423</v>
+        <v>-0.8676670418852268</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.702148753448988</v>
+        <v>-5.68991473626518</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>141</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.116490757804208</v>
+        <v>2.102760746130002</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.924508134914383</v>
+        <v>1.909541576004898</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.240303739730749</v>
+        <v>2.22343151410395</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.37216054993263</v>
+        <v>2.353963129940915</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>8.936352167616576</v>
+        <v>8.888857786234929</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.975295405788117</v>
+        <v>4.945566732264041</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>9.867025004837252</v>
+        <v>9.81641510690384</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.426755094106561</v>
+        <v>4.399249119184191</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.367314817086843</v>
+        <v>4.340712724140296</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.806278523959861</v>
+        <v>2.785075135702968</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.737800067742121</v>
+        <v>4.707517136589587</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.198256578898608</v>
+        <v>6.161705069897089</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.068157981089392</v>
+        <v>5.035328570605465</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.322162764100455</v>
+        <v>5.287575242150034</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>138</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.044162957891139</v>
+        <v>-1.044820048495957</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.656079817294255</v>
+        <v>-2.651617613591483</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.776615523060904</v>
+        <v>-3.767693854137974</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.0197086730606415</v>
+        <v>-0.02877724402748782</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.734471526387992</v>
+        <v>-2.733380021588147</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.9853221585988905</v>
+        <v>-0.9907723309211036</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.108968013028559</v>
+        <v>1.093352704347673</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.547228853117915</v>
+        <v>3.52104206210052</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>9.301052029705495</v>
+        <v>9.249340965637238</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>9.906919382065766</v>
+        <v>9.851251405570693</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.97944695727206</v>
+        <v>8.926851623538766</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>10.47310284245901</v>
+        <v>10.41347383435671</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>10.05666784933539</v>
+        <v>9.997870005935162</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>10.31285225611201</v>
+        <v>10.2521142492419</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>141</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.6980510414921497</v>
+        <v>0.6889657078930824</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2037760675458813</v>
+        <v>-0.2106224625566568</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.66012419888996</v>
+        <v>3.634277144757654</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.082925200630328</v>
+        <v>3.058033679623712</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.125649334077416</v>
+        <v>1.108329232621188</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.556115824084131</v>
+        <v>3.528310800579042</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.184669230937587</v>
+        <v>4.152685968415838</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.429777470875599</v>
+        <v>4.396658510525008</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.660165792575768</v>
+        <v>3.630198594956035</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.7473878660398938</v>
+        <v>-0.7576609998684773</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.663134518593019</v>
+        <v>-1.670074827935743</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.220872037447236</v>
+        <v>1.199501614506822</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.513777065944431</v>
+        <v>1.48991941518932</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.767461586594308</v>
+        <v>1.741475951369722</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>141</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.95337019042816</v>
+        <v>4.921745443662971</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>6.18174706288206</v>
+        <v>6.14182337655955</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.919197051178024</v>
+        <v>7.868950925260371</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.18405027706087</v>
+        <v>10.12047727828273</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>11.0708034652416</v>
+        <v>11.0012359836004</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>10.66332680070251</v>
+        <v>10.59648955004647</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>11.29510197960096</v>
+        <v>11.22361135502195</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>10.12100814354473</v>
+        <v>10.05544154084021</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>10.0651227547142</v>
+        <v>9.999440919151446</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>10.64082282709606</v>
+        <v>10.57177096945496</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>9.729332660911311</v>
+        <v>9.663958067858502</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>10.48238750728267</v>
+        <v>10.41178571347922</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>11.49190017644411</v>
+        <v>11.41491033801388</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>11.03709904014234</v>
+        <v>10.96133410739809</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>138</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-5.391989044847655</v>
+        <v>-5.371899237822355</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-12.80505395029474</v>
+        <v>-12.74798598859766</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-12.47906611486373</v>
+        <v>-12.42595472965906</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-15.979776321392</v>
+        <v>-15.91067735345377</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-18.7013092235792</v>
+        <v>-18.61958940580613</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-20.58828135311882</v>
+        <v>-20.49560283708065</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-22.13239782120916</v>
+        <v>-22.03326638276224</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-24.78894630510209</v>
+        <v>-24.67527985197156</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-29.22084342018855</v>
+        <v>-29.0838946680344</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-27.90223761265372</v>
+        <v>-27.77302020386105</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-30.30011403471771</v>
+        <v>-30.15884529625568</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-25.17943193935086</v>
+        <v>-25.06735646881901</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-28.52177543257834</v>
+        <v>-28.39353991380898</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-29.73662538105788</v>
+        <v>-29.60295821452621</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>141</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.42960853297577</v>
+        <v>-1.429573723982131</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.170431276844766</v>
+        <v>-5.149767043169241</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.147157676953825</v>
+        <v>-4.134892396257754</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-8.98828294224338</v>
+        <v>-8.950468728291355</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-10.2406220706855</v>
+        <v>-10.19699273077596</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-12.78959033123858</v>
+        <v>-12.72990686863463</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-11.45627423488909</v>
+        <v>-11.4056932268904</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-14.06363814624265</v>
+        <v>-13.997029825765</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-15.5539947694572</v>
+        <v>-15.47797233036923</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-17.12454253885033</v>
+        <v>-17.04078532180314</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-15.91192595648518</v>
+        <v>-15.83515370862436</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-20.15605812654895</v>
+        <v>-20.05885150848027</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-22.01116827507423</v>
+        <v>-21.90427840213732</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-23.19402093022166</v>
+        <v>-23.08121908409095</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>138</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-7.56590208832592</v>
+        <v>-7.528776843289116</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-7.731186567437824</v>
+        <v>-7.692365597373289</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-7.403590915543496</v>
+        <v>-7.370053833166544</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-5.82434835712273</v>
+        <v>-5.800751244013895</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-9.995221797998738</v>
+        <v>-9.947416548144794</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-8.975499644569631</v>
+        <v>-8.93112603452694</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-9.062863511833669</v>
+        <v>-9.020186845149482</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-9.536134226511336</v>
+        <v>-9.488249211260694</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.147378955524005</v>
+        <v>-8.106259233811841</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-10.45909308077756</v>
+        <v>-10.40475593783498</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-10.66856751065734</v>
+        <v>-10.61352664477806</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-10.63608140314471</v>
+        <v>-10.58380228436117</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-11.06248477636491</v>
+        <v>-11.00790109168189</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-13.73117164902881</v>
+        <v>-13.66092922901914</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>141</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6980510414923202</v>
+        <v>0.6868810391050459</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.332677197032531</v>
+        <v>-2.323383376802319</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.857833204234488</v>
+        <v>-4.83610607422753</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.728803648720863</v>
+        <v>-4.709016727975978</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-5.270006284722371</v>
+        <v>-5.246126476143928</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-9.240631136699051</v>
+        <v>-9.188383423870576</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-10.75118002049305</v>
+        <v>-10.69166011768121</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-13.36123676728488</v>
+        <v>-13.28196555686751</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-14.85349975195492</v>
+        <v>-14.76329944680448</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-16.42689805795059</v>
+        <v>-16.32642085153314</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-16.64001498454491</v>
+        <v>-16.53871281580957</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-19.46327094003939</v>
+        <v>-19.34664389184297</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-19.18147150010569</v>
+        <v>-19.06680041470841</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-19.65341534928415</v>
+        <v>-19.5351197933108</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>147</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.473030156944823</v>
+        <v>-1.470777134698565</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-12.61475781890127</v>
+        <v>-12.53227899152635</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-8.929880212917759</v>
+        <v>-8.87637958610209</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-9.484598709010243</v>
+        <v>-9.428567038422251</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-10.02879050277819</v>
+        <v>-9.968012369075851</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-10.41928482141932</v>
+        <v>-10.35073553092251</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-14.60341002428155</v>
+        <v>-14.50780814505559</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-12.35086777023705</v>
+        <v>-12.26639242045398</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-15.83604949747183</v>
+        <v>-15.72504895905497</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-13.28162612051874</v>
+        <v>-13.18756388980644</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-14.17828885623006</v>
+        <v>-14.07850435527359</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-15.51833992854213</v>
+        <v>-15.41121127716234</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-17.31870650415685</v>
+        <v>-17.19930684782736</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-17.76242972152215</v>
+        <v>-17.63904221334312</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.048993875765603</v>
+        <v>-8.653128795628575</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.77018014470827</v>
+        <v>-4.111139428326183</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.103107266638126</v>
+        <v>1.25674872525984</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.177564846480792</v>
+        <v>2.439205573590229</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.098752605246979</v>
+        <v>-1.139514726546039</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.253285094442028</v>
+        <v>3.521468550870033</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.4234293181085746</v>
+        <v>0.444832903389802</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>5.276426184569004</v>
+        <v>5.674811207040477</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>7.445605360360616</v>
+        <v>7.97950086998528</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>9.457335086708241</v>
+        <v>10.17237812001109</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>10.23569229858315</v>
+        <v>11.01968497033018</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>8.7571141039179</v>
+        <v>9.429948420349348</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>7.494239166240625</v>
+        <v>8.048433693038355</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>8.71190737570187</v>
+        <v>9.357259663112316</v>
       </c>
     </row>
     <row r="23">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 27.82</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4094</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.02664933501281297</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 74.38</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3953~3966</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3953</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.2801370706120139</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 120.9</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3815~3828</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3815</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.1450151803124911</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 167.5</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3674~3687</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3674</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.2016021390328646</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 214.1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3533~3546</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3533</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.5193830466623126</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 260.6</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3395~3408</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3395</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.8795885549517592</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 307.2</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3254~3267</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3254</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-1.039505048094881</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 353.8</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3116~3129</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3116</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-1.039299617749123</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 400.3</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2975~2988</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2975</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-1.188217436675835</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 446.9</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2837~2850</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2837</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-1.195192706174886</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 493.5</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2696~2709</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2696</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.29373363213319</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 540</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2555~2568</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2555</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-1.636740500895328</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 586.6</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2417~2430</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2417</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.423479472473346</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 633.2</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2276~2289</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2276</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.423101928772667</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 679.7</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2138~2151</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2138</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.029003173766462</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 726.3</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1997~2010</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1997</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.150154738120428</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 772.8</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1850~1863</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1850</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.12467825579774</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 819.4</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1701~1701</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1701</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.4652196253246075</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 866</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1563~1563</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1563</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.158185601080099</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 912.5</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1422~1422</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1422</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.2491777135453006</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 959.1</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1281~1281</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1281</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.4339621481741034</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 1006</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1143~1143</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1143</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.4374453193350831</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 1052</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1002~1002</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1002</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.0982287393716561</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 1099</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>864~864</t>
-        </is>
+      <c r="B29" t="n">
+        <v>864</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.1786235053951586</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 1145</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>723~723</t>
-        </is>
+      <c r="B30" t="n">
+        <v>723</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.06534452902931065</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 1192</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>585~585</t>
-        </is>
+      <c r="B31" t="n">
+        <v>585</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.036476209704553</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 1238</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>444~444</t>
-        </is>
+      <c r="B32" t="n">
+        <v>444</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>2.686741859970205</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 1285</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>303~303</t>
-        </is>
+      <c r="B33" t="n">
+        <v>303</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>1.962007224344482</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 1332</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>178~178</t>
-        </is>
+      <c r="B34" t="n">
+        <v>178</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.000943702261935</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 1378</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>5.83989501312336</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 27.82</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-1.302962129733785</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 74.38</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>225~225</t>
-        </is>
+      <c r="B7" t="n">
+        <v>225</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-4.937882764654418</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 120.9</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>363~363</t>
-        </is>
+      <c r="B8" t="n">
+        <v>363</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-1.529250992386281</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 167.5</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>504~504</t>
-        </is>
+      <c r="B9" t="n">
+        <v>504</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1.474815648043993</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 214.1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>645~645</t>
-        </is>
+      <c r="B10" t="n">
+        <v>645</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>2.855398889092349</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 260.6</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>783~783</t>
-        </is>
+      <c r="B11" t="n">
+        <v>783</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>3.828400760249792</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 307.2</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>924~924</t>
-        </is>
+      <c r="B12" t="n">
+        <v>924</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>3.675392848621193</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 353.8</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1062~1062</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1062</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>3.062117235345582</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 400.3</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1203~1203</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1203</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2.951283209299582</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 446.9</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1341~1341</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1341</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>2.54011872676989</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 493.5</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1482~1482</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1482</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>2.364861274931727</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 540</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1623~1623</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1623</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>2.589740977387066</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 586.6</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1761~1761</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1761</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.964256171556066</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 633.2</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1902~1902</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1902</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.712660523112838</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 679.7</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2040~2040</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2040</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.084993052339044</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 726.3</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2181~2181</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2181</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.059977544072467</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 772.8</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2328~2328</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2328</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.9000324701680285</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 819.4</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2477~2490</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2477</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.3178066597097029</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 866</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2615~2628</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2615</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.09408070566522042</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 912.5</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2756~2769</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2756</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.1279634195238017</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 959.1</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2897~2910</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2897</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.1910328219281823</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 1006</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3035~3048</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3035</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.1640419947506544</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 1052</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3176~3189</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3176</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.03086396890887499</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 1099</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3314~3327</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3314</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.04638734856069249</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 1145</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3455~3468</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3455</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.01362286461597506</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 1192</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3593~3606</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3593</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.3303767561500734</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 1238</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3734~3747</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3734</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.3183649281630068</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 1285</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3875~3888</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3875</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.1529033407861036</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 1332</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4000~4013</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4000</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.08875354572703742</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 1378</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4094</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.1194427029711207</v>

--- a/workspaces/btc_daily_14days/cycle/days_since_halving.xlsx
+++ b/workspaces/btc_daily_14days/cycle/days_since_halving.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Days Since Halving is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Days Since Halving is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,105 +568,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 51.1</t>
+          <t>X ≈ 51.12</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>141</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.079996188559107</v>
+        <v>-7.067521686637434</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.567606947938181</v>
+        <v>-6.554741895792937</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-10.49891348651816</v>
+        <v>-10.48595060671041</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-16.03097496994977</v>
+        <v>-16.0180395826967</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-15.15705453200768</v>
+        <v>-15.14398290538354</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-19.11094381234167</v>
+        <v>-19.09793754991691</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-17.78420200354726</v>
+        <v>-17.77116736963619</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-17.54711428272903</v>
+        <v>-17.53396044064589</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-16.90394973681031</v>
+        <v>-16.89077356833307</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-15.63207437595878</v>
+        <v>-15.61868718129386</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-13.71459373067981</v>
+        <v>-13.70114958277118</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-15.81034915924912</v>
+        <v>-15.7969059019446</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-13.39841368049623</v>
+        <v>-13.38486201846672</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.478382204658971</v>
+        <v>-7.488811840356796</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 97.64</t>
+          <t>X ≈ 97.7</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>138</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.015571936500891</v>
+        <v>4.028052384440585</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.409602908609386</v>
+        <v>2.422471699379251</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.462359898108573</v>
+        <v>3.475329510005473</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.207424704338351</v>
+        <v>7.220372042243895</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.90119792954933</v>
+        <v>13.91428395737535</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.58600853680495</v>
+        <v>10.59902767192709</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12.67410165025891</v>
+        <v>12.68714798858511</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.48719332111768</v>
+        <v>11.50035661556411</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>11.42929767983014</v>
+        <v>11.44248150330442</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>14.20214106109525</v>
+        <v>14.2155348275973</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.82884667604776</v>
+        <v>11.84229491991233</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>12.59040479907185</v>
+        <v>12.60385114020935</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.72440838174915</v>
+        <v>10.73796131380999</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.078201205764131</v>
+        <v>8.067771570065979</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>141</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.176731714176555</v>
+        <v>9.189214210626318</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8.986409012043303</v>
+        <v>8.999280671783012</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.42428782068201</v>
+        <v>11.43726124062129</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12.26482069846687</v>
+        <v>12.27776971732909</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>13.14519713473726</v>
+        <v>13.15828142934188</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>12.030560731779</v>
+        <v>12.04357934933419</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>14.07279844009658</v>
+        <v>14.08584444397165</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>13.61009885955519</v>
+        <v>13.62326210281754</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>16.38603959372906</v>
+        <v>16.39922440515896</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>17.66631159935248</v>
+        <v>17.67970581974819</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>17.46650632919868</v>
+        <v>17.47995531766774</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>17.50554723825454</v>
+        <v>17.51899398290619</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>19.92614503077348</v>
+        <v>19.93969846196337</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>22.30885183789455</v>
+        <v>22.2984222021964</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>141</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.760950674121958</v>
+        <v>7.77342925730273</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.277271338612003</v>
+        <v>8.290139941262488</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.83567693568723</v>
+        <v>12.84864966280988</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15.79834685943624</v>
+        <v>15.81129702905745</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>13.85007830089519</v>
+        <v>13.86316171007415</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>16.27423534143404</v>
+        <v>16.28725531357321</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>16.19416467122962</v>
+        <v>16.20721083966824</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>17.85647415527291</v>
+        <v>17.86963850978749</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>19.92540241668615</v>
+        <v>19.93858802181627</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>21.91531115667608</v>
+        <v>21.92870629390163</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>26.67742915091311</v>
+        <v>26.69088000346494</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>29.55472167079395</v>
+        <v>29.56817011220149</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>31.97904599195143</v>
+        <v>31.99260029984633</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>31.52870999392292</v>
+        <v>31.51828035822445</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>138</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8.342194494226639</v>
+        <v>8.354670859555</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.460624756066004</v>
+        <v>7.473489839124859</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>6.347064893525229</v>
+        <v>6.360029605366535</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.923934668170098</v>
+        <v>7.936876735444599</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.111468290665371</v>
+        <v>8.124545861010212</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.242401365430197</v>
+        <v>6.25541341087655</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.990324338243916</v>
+        <v>4.003362250066616</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.248649207443755</v>
+        <v>4.261805867287151</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.018514547982299</v>
+        <v>2.031692007090463</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.169872991340107</v>
+        <v>1.183260729522281</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.413917178258373</v>
+        <v>2.427361747684436</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.173564155675024</v>
+        <v>3.187008115367711</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.927981560368679</v>
+        <v>4.94153360156659</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.078201205763804</v>
+        <v>8.067771570065823</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>141</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.810966542124305</v>
+        <v>2.823433115156945</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.09878283695122</v>
+        <v>11.11164895682533</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>11.41587218468611</v>
+        <v>11.42883911307357</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>15.08446747634814</v>
+        <v>15.09741377907556</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11.72261443969408</v>
+        <v>11.73569285867912</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>15.56127193144039</v>
+        <v>15.57428879539336</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>16.18955868473441</v>
+        <v>16.2026024799861</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>17.14422525652886</v>
+        <v>17.15738736443431</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>13.54837555095289</v>
+        <v>13.56155673746878</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>13.41174909921114</v>
+        <v>13.42514004129531</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>12.50300394263125</v>
+        <v>12.5164503651055</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>11.12404217562215</v>
+        <v>11.13748699342091</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8.580716087982744</v>
+        <v>8.594268182032565</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.415234816617954</v>
+        <v>7.404805180919638</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>138</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.044143605757114</v>
+        <v>-1.031686715909366</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.4856214735103563</v>
+        <v>-0.4727722356001465</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.73172548435268</v>
+        <v>2.744680219663692</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.6951362526618894</v>
+        <v>0.7080662735292975</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.8811391772258546</v>
+        <v>0.894205719858121</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2666922736883635</v>
+        <v>-0.2536895661163925</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.519804724632145</v>
+        <v>-2.506775326127531</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.2632947972984</v>
+        <v>-2.250145378551295</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.153508643850742</v>
+        <v>-0.1403354251146496</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2787460383990208</v>
+        <v>-0.2653614748109021</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2410654631153406</v>
+        <v>0.2545075004265982</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.172188915978779</v>
+        <v>-1.158747072226838</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.8676670418852268</v>
+        <v>-0.8541161810178295</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.68991473626518</v>
+        <v>-5.700344371963496</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>141</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.102760746130002</v>
+        <v>2.115216131398348</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.909541576004898</v>
+        <v>1.922388510651409</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.22343151410395</v>
+        <v>2.236381189922938</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.353963129940915</v>
+        <v>2.366890670265754</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>8.888857786234929</v>
+        <v>8.901928556053775</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.945566732264041</v>
+        <v>4.95857050228291</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>9.81641510690384</v>
+        <v>9.829450737875746</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.399249119184191</v>
+        <v>4.412400066999112</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.340712724140296</v>
+        <v>4.35388616522031</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.785075135702968</v>
+        <v>2.798459225542459</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.707517136589587</v>
+        <v>4.720959328469895</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.161705069897089</v>
+        <v>6.17514761063299</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.035328570605465</v>
+        <v>5.048879627592662</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.287575242150034</v>
+        <v>5.277145606451882</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>138</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.044820048495957</v>
+        <v>-1.03237579590062</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.651617613591483</v>
+        <v>-2.638783126787374</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.767693854137974</v>
+        <v>-3.754757465688577</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.02877724402748782</v>
+        <v>-0.01585722447870808</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.733380021588147</v>
+        <v>-2.720324989748356</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.9907723309211036</v>
+        <v>-0.9777776462317362</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.093352704347673</v>
+        <v>1.10637870890509</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.52104206210052</v>
+        <v>3.534189846763283</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>9.249340965637238</v>
+        <v>9.262515320958968</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>9.851251405570693</v>
+        <v>9.864637161469474</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.926851623538766</v>
+        <v>8.940294144742239</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>10.41347383435671</v>
+        <v>10.42691666759111</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>9.997870005935162</v>
+        <v>10.01142127621505</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>10.2521142492419</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>141</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.6889657078930824</v>
+        <v>0.7014050364651183</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2106224625566568</v>
+        <v>-0.1977918799039031</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.634277144757654</v>
+        <v>3.647217108687911</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.058033679623712</v>
+        <v>3.070952101915701</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.108329232621188</v>
+        <v>1.12138322453491</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.528310800579042</v>
+        <v>3.541305598316093</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.152685968415838</v>
+        <v>4.1657110794212</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.396658510525008</v>
+        <v>4.409804049456078</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.630198594956035</v>
+        <v>3.643367337377107</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.7576609998684773</v>
+        <v>-0.7442824162632675</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.670074827935743</v>
+        <v>-1.656637735362921</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.199501614506822</v>
+        <v>1.212941289528615</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.48991941518932</v>
+        <v>1.503469195390757</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.741475951369722</v>
+        <v>1.73104631567157</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>141</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.921745443662971</v>
+        <v>4.934184439180299</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>6.14182337655955</v>
+        <v>6.154657148812475</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.868950925260371</v>
+        <v>7.881891553053386</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.12047727828273</v>
+        <v>10.13340062337782</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>11.0012359836004</v>
+        <v>11.01429783132281</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>10.59648955004647</v>
+        <v>10.60948842580164</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>11.22361135502195</v>
+        <v>11.23664023925669</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>10.05544154084021</v>
+        <v>10.06858902090922</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>9.999440919151446</v>
+        <v>10.0126117222424</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>10.57177096945496</v>
+        <v>10.5851536938178</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>9.663958067858502</v>
+        <v>9.677398203851666</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>10.41178571347922</v>
+        <v>10.42522695886617</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>11.41491033801388</v>
+        <v>11.42846102554351</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>10.96133410739809</v>
+        <v>10.95090447170011</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>138</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-5.371899237822355</v>
+        <v>-5.35949107472959</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-12.74798598859766</v>
+        <v>-12.73519779048718</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-12.42595472965906</v>
+        <v>-12.41305774569701</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-15.91067735345377</v>
+        <v>-15.89780245267819</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-18.61958940580613</v>
+        <v>-18.60657634105371</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-20.49560283708065</v>
+        <v>-20.48264948699676</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-22.03326638276224</v>
+        <v>-22.02027968395746</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-24.67527985197156</v>
+        <v>-24.66217035771293</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-29.0838946680344</v>
+        <v>-29.07075924626712</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-27.77302020386105</v>
+        <v>-27.75966524846795</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-30.15884529625568</v>
+        <v>-30.14542683474662</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-25.06735646881901</v>
+        <v>-25.05392810991368</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-28.39353991380898</v>
+        <v>-28.3799963704206</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-29.60295821452621</v>
+        <v>-29.61338785022437</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>141</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.429573723982131</v>
+        <v>-1.417170707753492</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.149767043169241</v>
+        <v>-5.136978987548133</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.134892396257754</v>
+        <v>-4.121993737930644</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-8.950468728291355</v>
+        <v>-8.937596021751212</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-10.19699273077596</v>
+        <v>-10.1839800592966</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-12.72990686863463</v>
+        <v>-12.71695556614164</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-11.4056932268904</v>
+        <v>-11.39270480017161</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-13.997029825765</v>
+        <v>-13.98391955776896</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-15.47797233036923</v>
+        <v>-15.46483438112504</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-17.04078532180314</v>
+        <v>-17.02743037092996</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-15.83515370862436</v>
+        <v>-15.82173347096571</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-20.05885150848027</v>
+        <v>-20.04542507537625</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-21.90427840213732</v>
+        <v>-21.89073566926442</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-23.08121908409095</v>
+        <v>-23.09164871978926</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>138</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-7.528776843289116</v>
+        <v>-7.516406525818354</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-7.692365597373289</v>
+        <v>-7.679601125860721</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-7.370053833166544</v>
+        <v>-7.357177622843302</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-5.800751244013895</v>
+        <v>-5.787887266823773</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-9.947416548144794</v>
+        <v>-9.934417968887793</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-8.93112603452694</v>
+        <v>-8.918182246343591</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-9.020186845149482</v>
+        <v>-9.007206553431217</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-9.488249211260694</v>
+        <v>-9.475144115896768</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.106259233811841</v>
+        <v>-8.093122933918195</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-10.40475593783498</v>
+        <v>-10.39140329540356</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-10.61352664477806</v>
+        <v>-10.60010889250878</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-10.58380228436117</v>
+        <v>-10.57037599221681</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-11.00790109168189</v>
+        <v>-10.99435821437283</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-13.66092922901914</v>
+        <v>-13.67135886471712</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>141</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6868810391050459</v>
+        <v>0.6992542879539556</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.323383376802319</v>
+        <v>-2.310625518965757</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.83610607422753</v>
+        <v>-4.823243071444949</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.709016727975978</v>
+        <v>-4.696167292706434</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-5.246126476143928</v>
+        <v>-5.233135244689677</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-9.188383423870576</v>
+        <v>-9.175455835469869</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-10.69166011768121</v>
+        <v>-10.67869631124717</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-13.28196555686751</v>
+        <v>-13.26887825887083</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-14.76329944680448</v>
+        <v>-14.7501812685512</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-16.32642085153314</v>
+        <v>-16.31308261485594</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-16.53871281580957</v>
+        <v>-16.52530591198924</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-19.34664389184297</v>
+        <v>-19.33322617606168</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-19.06680041470841</v>
+        <v>-19.05326168761043</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-19.5351197933108</v>
+        <v>-19.54554942900912</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>147</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.470777134698565</v>
+        <v>-1.45843411480994</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-12.53227899152635</v>
+        <v>-12.51958088543009</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-8.87637958610209</v>
+        <v>-8.863553314959312</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-9.428567038422251</v>
+        <v>-9.415752657547898</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-9.968012369075851</v>
+        <v>-9.955053386006476</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-10.35073553092251</v>
+        <v>-10.33783120256169</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-14.50780814505559</v>
+        <v>-14.49487067540434</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-12.26639242045398</v>
+        <v>-12.25332094947094</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-15.72504895905497</v>
+        <v>-15.7119475919932</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-13.18756388980644</v>
+        <v>-13.17423497429461</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-14.07850435527359</v>
+        <v>-14.06510509010394</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-15.41121127716234</v>
+        <v>-15.39779814622418</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-17.19930684782736</v>
+        <v>-17.18577101040565</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-17.63904221334312</v>
+        <v>-17.64947184904112</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.653128795628575</v>
+        <v>-8.930486845985094</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-4.111139428326183</v>
+        <v>-4.42919283750043</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.25674872525984</v>
+        <v>0.900165517783563</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.439205573590229</v>
+        <v>2.075377427819902</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.139514726546039</v>
+        <v>-1.483109960871218</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.521468550870033</v>
+        <v>3.148536165566817</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.444832903389802</v>
+        <v>0.09167623690017734</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>5.674811207040477</v>
+        <v>5.283613489981832</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>7.97950086998528</v>
+        <v>7.572361733808002</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>10.17237812001109</v>
+        <v>9.744967296929218</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>11.01968497033018</v>
+        <v>10.58510893504148</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>9.429948420349348</v>
+        <v>9.00598648689526</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>8.048433693038355</v>
+        <v>7.630779776852407</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>9.357259663112316</v>
+        <v>9.57501794687709</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>138</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.942713682528733</v>
+        <v>-3.930191392853111</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-9.902113382449677</v>
+        <v>-9.889203572873626</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-15.36944585716221</v>
+        <v>-15.3564387257446</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-19.58701881151131</v>
+        <v>-19.57403966911285</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-20.85007770774282</v>
+        <v>-20.83696690336788</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-22.00191113234592</v>
+        <v>-21.98886823605155</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-22.81128253077762</v>
+        <v>-22.79821627647715</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-23.2784659295592</v>
+        <v>-23.26528492026396</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-25.51337885921968</v>
+        <v>-25.50018012026492</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-27.08814172540711</v>
+        <v>-27.07473659775428</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-29.46680809320286</v>
+        <v>-29.45335079949265</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-32.33097566049504</v>
+        <v>-32.31752337177493</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-34.92514331491836</v>
+        <v>-34.91158726856676</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-36.12469734496075</v>
+        <v>-36.1351269806589</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>141</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.266487965600049</v>
+        <v>-4.253965675924427</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-4.459621862252249</v>
+        <v>-4.446712052676197</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-6.982150143316844</v>
+        <v>-6.969143011899241</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.724237436241253</v>
+        <v>-4.711258293842789</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-5.971878509469455</v>
+        <v>-5.958767705094516</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-5.674436571753873</v>
+        <v>-5.661393675459507</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.503851140090063</v>
+        <v>-1.490784885789587</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.389474255183622</v>
+        <v>-3.376293245888384</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.159693999521785</v>
+        <v>-4.146495260567022</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-6.428258900861771</v>
+        <v>-6.414853773208939</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.342232083335382</v>
+        <v>-7.328774789625164</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-10.14472835861423</v>
+        <v>-10.13127606989412</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-14.11108226033919</v>
+        <v>-14.09752621398759</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-13.15214106990695</v>
+        <v>-13.16257070560511</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>141</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.429608532975934</v>
+        <v>-1.417086243300311</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9135225714721074</v>
+        <v>-0.9006127618960562</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.145270710692728</v>
+        <v>-4.132263579275126</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.724237436241253</v>
+        <v>-4.711258293842789</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.007339502377334</v>
+        <v>-0.9942286980023951</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.546776997285789</v>
+        <v>-3.533734100991424</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.922290856401951</v>
+        <v>-2.909224602101474</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.261814680715375</v>
+        <v>-1.248633671420137</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.09562514941422506</v>
+        <v>0.1088238883689883</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.6639396806984337</v>
+        <v>0.6773448083512648</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.877626072692827</v>
+        <v>1.891083366403045</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.330448946350394</v>
+        <v>3.343901235070504</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.874733342497699</v>
+        <v>7.888289388849302</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>9.542894391086037</v>
+        <v>9.532464755387885</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>138</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4051124044277046</v>
+        <v>0.4176346941033273</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>6.039915603057651</v>
+        <v>6.052825412633702</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.297220809504452</v>
+        <v>1.310227940922054</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.050662347909061</v>
+        <v>5.063641490307525</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.512241132836969</v>
+        <v>4.525351937211909</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.258958432871481</v>
+        <v>6.272001329165846</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.072775440236867</v>
+        <v>9.085841694537343</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>13.61705592338901</v>
+        <v>13.63025466234377</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>16.39011914415819</v>
+        <v>16.40352427181102</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>15.46072813868119</v>
+        <v>15.47418543239141</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>17.66902433950487</v>
+        <v>17.68247662822498</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>17.97340740971932</v>
+        <v>17.98696345607092</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>18.22312874199568</v>
+        <v>18.21269910629753</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>141</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.244150332272376</v>
+        <v>4.256672621947999</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>12.56165473349252</v>
+        <v>12.57456454306858</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>10.03912645242768</v>
+        <v>10.05213358384528</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>13.7154788758154</v>
+        <v>13.72845801821386</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>14.5954973770553</v>
+        <v>14.60860818143023</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>14.89293931477096</v>
+        <v>14.90598221106532</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>15.5174254556547</v>
+        <v>15.53049170995517</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>13.63180234056114</v>
+        <v>13.64498334985638</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>16.40768188700287</v>
+        <v>16.42088062595764</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>19.10365599275509</v>
+        <v>19.11706112040793</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>21.02656224290567</v>
+        <v>21.04001953661589</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>21.77016525840713</v>
+        <v>21.78361754712724</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>22.76835036377437</v>
+        <v>22.78190641012597</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>23.7272915542066</v>
+        <v>23.71686191850845</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>138</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4051124044276193</v>
+        <v>0.4176346941032421</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.692089516101042</v>
+        <v>1.704999325677093</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.297220809504623</v>
+        <v>1.310227940922225</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.7028362609525729</v>
+        <v>0.7158154033510371</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.062965770518133</v>
+        <v>3.076076574893072</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.80968307055263</v>
+        <v>4.822725966846996</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.551036309802093</v>
+        <v>2.564102564102569</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.0900601324576229</v>
+        <v>-0.0768791231623851</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.5735776625195754</v>
+        <v>0.5867764014743386</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.346640883288664</v>
+        <v>3.360046010941495</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.2433368343333626</v>
+        <v>0.2567941280435804</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.171555370640043</v>
+        <v>-1.158103081919933</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.8671723004255227</v>
+        <v>-0.8536162540739198</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.556462075329023</v>
+        <v>1.546032439630871</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>141</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.429608532975969</v>
+        <v>-1.417086243300346</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.5049171448399505</v>
+        <v>0.5178269544160017</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.563710427004864</v>
+        <v>-5.550703295587262</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.724237436241296</v>
+        <v>-4.711258293842832</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-4.553438793157483</v>
+        <v>-4.540327988782543</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.546776997285789</v>
+        <v>-3.533734100991424</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-4.340730572714101</v>
+        <v>-4.327664318413625</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.261814680715496</v>
+        <v>-1.248633671420258</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4.868913857677903</v>
+        <v>-4.85571511872314</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-5.719039042705788</v>
+        <v>-5.705633915052957</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-5.923792367023445</v>
+        <v>-5.910335073313227</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-9.435508500458113</v>
+        <v>-9.422056211738003</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-9.146543253246989</v>
+        <v>-9.132987206895386</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-12.44292121175084</v>
+        <v>-12.45335084744899</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>138</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-8.290539769485299</v>
+        <v>-8.278017479809677</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-12.07602642592786</v>
+        <v>-12.06311661635181</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-10.29698208904618</v>
+        <v>-10.28397495762858</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-14.51455504339525</v>
+        <v>-14.50157590099678</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-15.05297625846737</v>
+        <v>-15.03986545409244</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-14.75553432075171</v>
+        <v>-14.74249142445735</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-19.18809412498052</v>
+        <v>-19.17502787068004</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-20.37991520492144</v>
+        <v>-20.3667341956262</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-20.44091509110378</v>
+        <v>-20.42771635214901</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-24.91422868192877</v>
+        <v>-24.90082355427594</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-26.56825736856514</v>
+        <v>-26.55480007485492</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-26.53387421121971</v>
+        <v>-26.5204219224996</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-22.6063027352081</v>
+        <v>-22.59274668885649</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-25.25513212756949</v>
+        <v>-25.26556176326764</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>141</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.0111688166638757</v>
+        <v>0.001353473011747042</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.9135225714721074</v>
+        <v>-0.9006127618960562</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5991714199126648</v>
+        <v>-0.5861642884950626</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.305797719929195</v>
+        <v>-3.292818577530731</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.42577921868935</v>
+        <v>-2.41266841431441</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.419117422817706</v>
+        <v>-1.406074526523341</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.042248150690163</v>
+        <v>2.055314404990639</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.8658448937526657</v>
+        <v>0.8790259030479035</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.932504582038412</v>
+        <v>2.945703320993175</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.500819113322585</v>
+        <v>3.514224240975416</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.714505505316978</v>
+        <v>4.727962799027196</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.748888662662374</v>
+        <v>4.762340951382484</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.619414193561489</v>
+        <v>3.632970239913092</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.159915667681744</v>
+        <v>3.149486031983592</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>141</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.244150332272298</v>
+        <v>4.256672621947921</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>8.306335584556265</v>
+        <v>8.319245394132317</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>12.17979315831344</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.87859944319124</v>
+        <v>10.89157858558971</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.630958369963054</v>
+        <v>9.644069174337993</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12.76527974030286</v>
+        <v>12.77832263659722</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>11.98439241917502</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12.21336262424905</v>
+        <v>12.22654363354429</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>14.98924217069089</v>
+        <v>15.00244090964566</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>17.68521627644306</v>
+        <v>17.69862140409589</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>17.48046295212558</v>
+        <v>17.4939202458358</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>21.06094540025114</v>
+        <v>21.07439768897125</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>22.05913050561826</v>
+        <v>22.07268655196987</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>25.14573127051865</v>
+        <v>25.1353016348205</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>125</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.90656167979003</v>
+        <v>1.919083969465653</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-3.705011933174234</v>
+        <v>-3.692102123598183</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.700119360229202</v>
+        <v>0.7131264916468041</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.769627507163321</v>
+        <v>-0.7566483647648568</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.091951277764522</v>
+        <v>1.105062082139462</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.989393215480163</v>
+        <v>3.002436111774529</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.104659498207887</v>
+        <v>2.117725752508363</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4.037476099426385</v>
+        <v>4.050657108721623</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>4.789674952198851</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.526351028216176</v>
+        <v>1.539756155869007</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.121597703898566</v>
+        <v>2.135054997608783</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>2.155980861244011</v>
+        <v>2.169433149964121</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>1.735726250299109</v>
+        <v>1.749282296650712</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.985447582575382</v>
+        <v>1.97501794687723</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>94</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.429608532975934</v>
+        <v>-1.417086243300311</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.341796577464059</v>
+        <v>3.35470638704011</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.946927870867484</v>
+        <v>2.959935002285086</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.141010790709018</v>
+        <v>4.153989933107482</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2.538759788402785</v>
+        <v>2.551870592777725</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.900031513352509</v>
+        <v>3.913074409646875</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.006787157782355</v>
+        <v>7.019853412082831</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.603433546234896</v>
+        <v>7.616614555530134</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8.606263447286643</v>
+        <v>8.619462186241407</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.692308475024682</v>
+        <v>6.705713602677513</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.80670408687733</v>
+        <v>11.82016138058755</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>15.03257660592486</v>
+        <v>15.04602889464497</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>15.67615178221401</v>
+        <v>15.68970782856562</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.9258731144903</v>
+        <v>15.91544347879215</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Days Since Halving is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Days Since Halving is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,157 +2210,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 27.82</t>
+          <t>X &gt; 27.84</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.02664933501281297</v>
+        <v>0.02638679322416237</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0865024348790584</v>
+        <v>-0.0867454155387648</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04335931150811234</v>
+        <v>0.04308265336134554</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08943682032206368</v>
+        <v>0.08914944278690484</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.07610921098410017</v>
+        <v>0.07582231605757528</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.003098252096620513</v>
+        <v>-0.00336452190813219</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.120558059534396</v>
+        <v>0.1202611011187997</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.08137853845078524</v>
+        <v>0.08108871076990454</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2534218097310372</v>
+        <v>0.2530895863451974</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.222105054570477</v>
+        <v>0.2217761607482345</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2751734910599168</v>
+        <v>0.2748304978528182</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2745355487440122</v>
+        <v>0.2741927301447404</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.234383148956006</v>
+        <v>0.2340479216507134</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2048906700204398</v>
+        <v>0.2050545769138736</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 74.38</t>
+          <t>X &gt; 74.4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3953</v>
+        <v>3954</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2801370706120139</v>
+        <v>0.2793562154953975</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1446728083137927</v>
+        <v>0.1439039278390339</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4193928213795317</v>
+        <v>0.4185489380528296</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.6644375950319841</v>
+        <v>0.6635332699475498</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.6194626356645614</v>
+        <v>0.618561955972396</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.678461632546572</v>
+        <v>0.677549690775038</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.7592049527533433</v>
+        <v>0.7582710693475505</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.7101712244579588</v>
+        <v>0.7092429673074889</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.8654100181960871</v>
+        <v>0.8644413073390353</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.7876095574049344</v>
+        <v>0.7866485257527742</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.7741760658803827</v>
+        <v>0.7732152199994999</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.8482691039747294</v>
+        <v>0.8472895705910162</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.7206529068494376</v>
+        <v>0.7196994900767493</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4789461912270596</v>
+        <v>0.4794185538575206</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 120.9</t>
+          <t>X &gt; 121</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3815</v>
+        <v>3816</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1450151803124911</v>
+        <v>0.1437901590712869</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.06274348882734415</v>
+        <v>0.06150289207579362</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3093195693248418</v>
+        <v>0.3080049865514027</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.4277581137517075</v>
+        <v>0.4264148866726813</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1390224074716215</v>
+        <v>0.1377418207015424</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.3200759253938514</v>
+        <v>0.3187541034063344</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.3282073788986253</v>
+        <v>0.326880866293358</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.3203339900309459</v>
+        <v>0.3189982913485281</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.4832824959665984</v>
+        <v>0.4819021178622975</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.302365691740647</v>
+        <v>0.3010127003716079</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.3742954514103616</v>
+        <v>0.3729183126127182</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4235208140865581</v>
+        <v>0.4221308974759026</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3587870469448049</v>
+        <v>0.3574038580863999</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.2040583296265126</v>
+        <v>0.2049969825166542</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3674</v>
+        <v>3675</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2016021390328646</v>
+        <v>-0.2032587637230705</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2797270715355964</v>
+        <v>-0.2814159288599143</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.117248346690765</v>
+        <v>-0.1189950493190395</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.02652218685930308</v>
+        <v>-0.02829015580964267</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3601258332862614</v>
+        <v>-0.3618217397932355</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1293465998375964</v>
+        <v>-0.1310963346006986</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1992796487630386</v>
+        <v>-0.2010140628093993</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1896978136170944</v>
+        <v>-0.1914510140710988</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.127030174361245</v>
+        <v>-0.1288033086707117</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.3640241756990079</v>
+        <v>-0.3657616478820245</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2816658261530947</v>
+        <v>-0.2834333112547114</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2320496066558704</v>
+        <v>-0.2338303800875536</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3921649061634724</v>
+        <v>-0.3939168328378599</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.6442747908595479</v>
+        <v>-0.6426691279526935</v>
       </c>
     </row>
     <row r="10">
@@ -2422,101 +2422,101 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3533</v>
+        <v>3534</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5193830466623126</v>
+        <v>-0.5215137187215575</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.6212319613829749</v>
+        <v>-0.6234050000787192</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6341921521861735</v>
+        <v>-0.6363798553207829</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.6580836178040173</v>
+        <v>-0.6602601029138455</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.9272469153467213</v>
+        <v>-0.929372013259929</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.7840041299024918</v>
+        <v>-0.7861579029064387</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8535325921875909</v>
+        <v>-0.8556715928742946</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.9099101678807529</v>
+        <v>-0.9120547556851548</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.9273112372929404</v>
+        <v>-0.9294547454558497</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.253179647497724</v>
+        <v>-1.25526928223163</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.357587816463408</v>
+        <v>-1.359658036035533</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.420822533381163</v>
+        <v>-1.422874542343564</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.684081333175705</v>
+        <v>-1.686078382274324</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.928280127585936</v>
+        <v>-1.925830949557387</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 260.6</t>
+          <t>X &gt; 260.7</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.8795885549517592</v>
+        <v>-0.8822067316197177</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.9497433684545413</v>
+        <v>-0.9524307620958297</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9179663708336534</v>
+        <v>-0.9206862468328154</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.00692559820591</v>
+        <v>-1.009613720020283</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.294652717535136</v>
+        <v>-1.297287403910481</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.069613543262115</v>
+        <v>-1.07229949339586</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.050425745766248</v>
+        <v>-1.053123498152814</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.119595350147257</v>
+        <v>-1.122299975346571</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.047053198520622</v>
+        <v>-1.04978403045331</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.351671919709695</v>
+        <v>-1.354361491189827</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.510891995924851</v>
+        <v>-1.513547532547122</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.607575217649128</v>
+        <v>-1.61020192949438</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.952848543576039</v>
+        <v>-1.955398303879164</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.335023698720626</v>
+        <v>-2.331931405301795</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3254</v>
+        <v>3255</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.039505048094881</v>
+        <v>-1.042727536042307</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.471821486144222</v>
+        <v>-1.475022233791023</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.452407439158264</v>
+        <v>-1.455642644911705</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.704186330692735</v>
+        <v>-1.707337491870518</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.858707625085628</v>
+        <v>-1.861849682566437</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.79025117446465</v>
+        <v>-1.793395944615298</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.797456417155495</v>
+        <v>-1.800606558956993</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.910990158242321</v>
+        <v>-1.914138966102051</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.67949187512658</v>
+        <v>-1.682717685837957</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.9913899171491</v>
+        <v>-1.994579529924202</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.118132108812503</v>
+        <v>-2.12129859355143</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.159252553989404</v>
+        <v>-2.162405965786569</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.409281430192443</v>
+        <v>-2.412388465020044</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.757514925107451</v>
+        <v>-2.753707091525214</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3116</v>
+        <v>3117</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.039299617749123</v>
+        <v>-1.043216350023165</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.515497866678068</v>
+        <v>-1.51939518847513</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.637712427426727</v>
+        <v>-1.641604966153736</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.810446445103175</v>
+        <v>-1.81427548340892</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.980048722235495</v>
+        <v>-1.983869459767142</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.857725862624825</v>
+        <v>-1.861563888225461</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.765465381715259</v>
+        <v>-1.769342109207379</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.895387449580653</v>
+        <v>-1.899262840045587</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.747073930940466</v>
+        <v>-1.751004099690959</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.067238715373584</v>
+        <v>-2.071137788379652</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.222615184847811</v>
+        <v>-2.226483463929668</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.202967182373698</v>
+        <v>-2.206841296974005</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.477555751625815</v>
+        <v>-2.481378383272315</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.62764612730907</v>
+        <v>-2.623249618089062</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.188217436675835</v>
+        <v>-1.192859824445357</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.677827467154813</v>
+        <v>-1.682463569381319</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.820711182302631</v>
+        <v>-1.825340197338825</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.007818461937198</v>
+        <v>-2.012375089480201</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.495180089527715</v>
+        <v>-2.499628035113489</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.180167629306958</v>
+        <v>-2.184695255517688</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.314388120839723</v>
+        <v>-2.318881689663939</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.193721485276733</v>
+        <v>-2.198303320520488</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.035604323668657</v>
+        <v>-2.040247892484139</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.297213926466625</v>
+        <v>-2.301854582386042</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.551068515040306</v>
+        <v>-2.555646580101836</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.599410472313259</v>
+        <v>-2.603971819814255</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.833628588410562</v>
+        <v>-2.838154720480624</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.002787711542254</v>
+        <v>-2.997562698284042</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.195192706174886</v>
+        <v>-1.200663487566977</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.630459458621758</v>
+        <v>-1.635961772720989</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.726004235276442</v>
+        <v>-1.73152075300046</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.104084830661748</v>
+        <v>-2.109457353528896</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.483593346269217</v>
+        <v>-2.488896470723212</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.238023304730731</v>
+        <v>-2.243382581127783</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.480150628374389</v>
+        <v>-2.485437692131349</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.471704343767421</v>
+        <v>-2.477050345568109</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.584537157621504</v>
+        <v>-2.589853714702308</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.888150907721887</v>
+        <v>-2.893459889169712</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.109388211594379</v>
+        <v>-3.114645811965289</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.232395327554862</v>
+        <v>-3.237609103557006</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.457790310659313</v>
+        <v>-3.462975540615936</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.647545015239196</v>
+        <v>-3.641331595053693</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2696</v>
+        <v>2697</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.29373363213319</v>
+        <v>-1.300104222416273</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.704716512199347</v>
+        <v>-1.711149742645794</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.006345360864287</v>
+        <v>-2.012722843656029</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.374062096963769</v>
+        <v>-2.380290773335233</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.67144983129279</v>
+        <v>-2.677643017638822</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.539600867360065</v>
+        <v>-2.545807880831752</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.827046014185754</v>
+        <v>-2.83316182145613</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.830917682957036</v>
+        <v>-2.837097238300203</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.909565993346064</v>
+        <v>-2.915728452686423</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.999574897709763</v>
+        <v>-3.005819556830012</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.184663874463773</v>
+        <v>-3.190870928317125</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.464182222521742</v>
+        <v>-3.470285264263374</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.716554061158064</v>
+        <v>-3.722622818249214</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.929389212676824</v>
+        <v>-3.92220118549205</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.636740500895328</v>
+        <v>-1.64401451243392</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.137734956158255</v>
+        <v>-2.145061625155819</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.551322572740432</v>
+        <v>-2.558552511080137</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.063584622173067</v>
+        <v>-3.070600040524795</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.425989439864196</v>
+        <v>-3.432949613766986</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-3.264527970629857</v>
+        <v>-3.27151084610378</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.602444326928719</v>
+        <v>-3.609312874101079</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.542063143057014</v>
+        <v>-3.549030635228412</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.621961286755912</v>
+        <v>-3.628911537453632</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.748521969048397</v>
+        <v>-3.755556344131008</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.893726768345353</v>
+        <v>-3.9007402349039</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-4.229940139929234</v>
+        <v>-4.236821736666059</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-4.551597693362865</v>
+        <v>-4.558422044373927</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-4.751147329361984</v>
+        <v>-4.742665934186924</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.423479472473346</v>
+        <v>-1.431964981583299</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.531936593528286</v>
+        <v>-1.540661794380078</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.9875247913359</v>
+        <v>-1.996136579575946</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.330072500982851</v>
+        <v>-2.338526453726963</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.558502143505073</v>
+        <v>-2.566960991614152</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.28070987730333</v>
+        <v>-2.289237424911377</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.550125980339963</v>
+        <v>-2.558562907285456</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.335450025212488</v>
+        <v>-2.344062363225575</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.168197610042455</v>
+        <v>-2.176895415114394</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.376829475707844</v>
+        <v>-2.385594793759417</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.394104775440255</v>
+        <v>-2.402904523250349</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.040215914283067</v>
+        <v>-3.048748668217691</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.190328340271613</v>
+        <v>-3.198878100207494</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.332218946179253</v>
+        <v>-3.32324508041804</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.423101928772667</v>
+        <v>-1.432881096036532</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.307809135971432</v>
+        <v>-1.317964945791282</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.854493669941355</v>
+        <v>-1.864495885975593</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.91993371888686</v>
+        <v>-1.929888417235347</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.085291610638116</v>
+        <v>-2.095287874116025</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.633373859826314</v>
+        <v>-1.643515748181699</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.001516585891984</v>
+        <v>-2.011521182693031</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.61300593387773</v>
+        <v>-1.623280692417225</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.34364653993434</v>
+        <v>-1.354058614847602</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.468385813889107</v>
+        <v>-1.478919863420792</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.561421164025951</v>
+        <v>-1.571962546250852</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.985897979844665</v>
+        <v>-1.99625355473092</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.030984333802778</v>
+        <v>-2.041411294218463</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.108752768918457</v>
+        <v>-2.099114683777131</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.029003173766462</v>
+        <v>-1.040395584437704</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.8957096075928348</v>
+        <v>-0.9075368051416461</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.498484641632153</v>
+        <v>-1.51012932230671</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.669441287424021</v>
+        <v>-1.680985265648992</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.577820496804662</v>
+        <v>-1.589537545421074</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.16233092245087</v>
+        <v>-1.174182425719643</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.548487354938963</v>
+        <v>-1.560186642645412</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.104688079678084</v>
+        <v>-1.116708858644344</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.9071448786831198</v>
+        <v>-0.9192802716817496</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.891576142652184</v>
+        <v>-0.9039209323251285</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.9771412031542042</v>
+        <v>-0.98950149165357</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.430935026606456</v>
+        <v>-1.443084365215697</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.45155752716699</v>
+        <v>-1.463801815498826</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.363102464197283</v>
+        <v>-1.352518285006809</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.150154738120428</v>
+        <v>-1.163163668525399</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.7949074035575094</v>
+        <v>-0.8085200340459409</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.262828846942142</v>
+        <v>-1.276320994664815</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.454829300885301</v>
+        <v>-1.468202149625419</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.318816419144767</v>
+        <v>-1.332406776854079</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5956441910036148</v>
+        <v>-0.6095279959024396</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9029253321314314</v>
+        <v>-0.9166882125789186</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2449003359205904</v>
+        <v>-0.2591233304001364</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.07118150794938316</v>
+        <v>0.0567743031723893</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.1982150961821745</v>
+        <v>0.1835123996252435</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1215977038985727</v>
+        <v>0.10686909056232</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1659801192462353</v>
+        <v>-0.1805668500358806</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.2078172932444318</v>
+        <v>-0.222503596295752</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.08005066479566381</v>
+        <v>-0.06862569676640362</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.12467825579774</v>
+        <v>-1.139714313796155</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1377377982973087</v>
+        <v>0.1215318001806693</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.6578602206413251</v>
+        <v>-0.67376931930918</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.8212404103891231</v>
+        <v>-0.8370352535343315</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6315559842042902</v>
+        <v>-0.6476260899035609</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1794900938440023</v>
+        <v>0.1630601031677514</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1781113021928107</v>
+        <v>0.1616439441122424</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7103209270125959</v>
+        <v>0.6934142438858757</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.326341442354597</v>
+        <v>1.309071503922986</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.26184185885262</v>
+        <v>1.244338366111577</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.249930137789562</v>
+        <v>1.232358125979893</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.045397707896278</v>
+        <v>1.027932880131424</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.142317282173778</v>
+        <v>1.12466026641313</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.315177312305124</v>
+        <v>1.327584127320243</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1701</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.4652196253246075</v>
+        <v>-0.4526973356489847</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.5099204595359339</v>
+        <v>0.522830269111985</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.8255714099060398</v>
+        <v>-0.8125642784884377</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.106840911043399</v>
+        <v>-1.093861768644935</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5870610679145045</v>
+        <v>-0.5739502635395652</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1132522871653308</v>
+        <v>-0.1002093908709654</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1547476816294093</v>
+        <v>0.1678139359298854</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2754537596262665</v>
+        <v>0.2886347689215043</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.7435544025444969</v>
+        <v>0.7567531414992601</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.4813186942949415</v>
+        <v>0.4947238219477725</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.3941432653330352</v>
+        <v>0.407600559043253</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3109485273227932</v>
+        <v>0.3244008160429033</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.5373723408340823</v>
+        <v>0.5509283871856852</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.6107268300768709</v>
+        <v>0.6002971943787188</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1563</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.158185601080099</v>
+        <v>-0.1456633114044763</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.429217113530818</v>
+        <v>1.442126923106869</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.458532667970708</v>
+        <v>0.4715397993883101</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.5248062740267017</v>
+        <v>0.5377854164251659</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.2019960634331</v>
+        <v>1.215106867808039</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.81933563390627</v>
+        <v>1.832378530200636</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.182458602494521</v>
+        <v>2.195524856794997</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.355070469228053</v>
+        <v>2.368251478523291</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.06182490166379</v>
+        <v>3.075023640618554</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.91547450870241</v>
+        <v>2.928879636355241</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.030618817142347</v>
+        <v>3.044076110852565</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.192961027590776</v>
+        <v>3.206413316310886</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.668419788366926</v>
+        <v>3.681975834718529</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.854161594091707</v>
+        <v>3.843731958393555</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1422</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.2491777135453006</v>
+        <v>0.2617000032209233</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.013131526741383</v>
+        <v>2.026041336317434</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.196321891874746</v>
+        <v>1.209329023292348</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.045281072302217</v>
+        <v>1.058260214700681</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.913329618130192</v>
+        <v>1.926440422505131</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.562388996070887</v>
+        <v>2.575431892365252</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.54797876684362</v>
+        <v>2.561045021144096</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.924677224602206</v>
+        <v>2.937858233897444</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.777882683004982</v>
+        <v>3.791081421959746</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.841962842562154</v>
+        <v>3.855367970214985</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.059150446514607</v>
+        <v>4.072607740224825</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.515474532130092</v>
+        <v>4.528926820850202</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.431366194040322</v>
+        <v>5.444922240391925</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.540440550226592</v>
+        <v>5.53001091452844</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1281</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4339621481741034</v>
+        <v>0.4464844378497261</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.335269097270732</v>
+        <v>2.348178906846783</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.784272365693653</v>
+        <v>1.797279497111255</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.680333460830425</v>
+        <v>1.69331260322889</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.234826470749489</v>
+        <v>3.247869367043855</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.15009275347721</v>
+        <v>3.163159007777686</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.385485467107884</v>
+        <v>3.398666476403122</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.183189718318246</v>
+        <v>4.196388457273009</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.191768670682983</v>
+        <v>4.205173798335814</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.299271396326375</v>
+        <v>4.312728690036593</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.645910603632771</v>
+        <v>4.659362892352881</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.162424142570778</v>
+        <v>5.175980188922381</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.099889424886094</v>
+        <v>5.089459789187941</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1143</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4374453193350831</v>
+        <v>0.4499676090107059</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.887988941716408</v>
+        <v>1.900898751292459</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.843076490587883</v>
+        <v>1.856083622005485</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.273417112259253</v>
+        <v>1.286396254657717</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.959842791325315</v>
+        <v>1.972953595700254</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.869708176110088</v>
+        <v>2.882751072404453</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.435018203369744</v>
+        <v>2.44808445767022</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.405280123923326</v>
+        <v>2.418461133218564</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.044192748677155</v>
+        <v>3.057391487631918</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.719001946851328</v>
+        <v>2.73240707450416</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.951693941868832</v>
+        <v>2.96515123557905</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.073566163081281</v>
+        <v>3.087018451801391</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.615691254673571</v>
+        <v>3.629247301025174</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.515456331481779</v>
+        <v>3.505026695783627</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>1002</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.0982287393716561</v>
+        <v>-0.08570644969603336</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.3860060308976188</v>
+        <v>0.3989158404736699</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.6897401187122156</v>
+        <v>0.7027472501298178</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.4774119383010458</v>
+        <v>-0.4644327959025816</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1817716370459479</v>
+        <v>0.1948824414208872</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.177816369172781</v>
+        <v>1.190859265467147</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.5940806558925189</v>
+        <v>0.6071469101929949</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.825500051522198</v>
+        <v>0.8386810608174358</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.163701762146289</v>
+        <v>1.176900501101052</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4133769763199595</v>
+        <v>0.4267821039727906</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4082244504055694</v>
+        <v>0.4216817441157872</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4426076077510004</v>
+        <v>0.4560598964711104</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.9205565896204675</v>
+        <v>0.9341126359720704</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.6712759258887715</v>
+        <v>0.6608462901906194</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>864</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1786235053951586</v>
+        <v>-0.1661012157195358</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.1773954742331725</v>
+        <v>0.1903052838092236</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.592711952821773</v>
+        <v>0.6057190842393751</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6659238034596129</v>
+        <v>-0.6529446610611487</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2784190926058656</v>
+        <v>-0.2653082882309263</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.5977265488135046</v>
+        <v>0.61076944510787</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.2815113500597377</v>
+        <v>0.2945776043602137</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.9717353586856419</v>
+        <v>0.9849163679808797</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.257957694725562</v>
+        <v>1.271156433680325</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.05513045326531341</v>
+        <v>-0.04172532561248232</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.4345606668615432</v>
+        <v>0.4480179605717609</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.7004253056884551</v>
+        <v>0.7138775944085651</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.206096620669484</v>
+        <v>1.219652667021087</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.5298920270198408</v>
+        <v>0.5194623913216887</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>723</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.06534452902931065</v>
+        <v>0.07786681870493339</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.113521953409446</v>
+        <v>0.1264317629854972</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.793342043493354</v>
+        <v>1.806349174910956</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.125531552311088</v>
+        <v>0.1385106947095522</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.555298442356488</v>
+        <v>0.5684092467314272</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.405990725853613</v>
+        <v>1.419033622147978</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.182944422135968</v>
+        <v>1.196010676436444</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.407323955581298</v>
+        <v>1.420504964876535</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.452824760961924</v>
+        <v>2.466023499916687</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1.049449230152533</v>
+        <v>1.062854357805364</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.674571424507164</v>
+        <v>1.688028718217382</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.677142686970157</v>
+        <v>2.690594975690267</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.225076181142818</v>
+        <v>3.238632227494421</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.059859754083007</v>
+        <v>3.049430118384855</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>585</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.036476209704553</v>
+        <v>2.048998499380176</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.989005160842858</v>
+        <v>3.001914970418909</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.645418505528326</v>
+        <v>4.658425636945928</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.579090441554634</v>
+        <v>3.592069583953098</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.237250423063657</v>
+        <v>4.250361227438596</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.218453044539999</v>
+        <v>5.231495940834364</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.988420181968571</v>
+        <v>6.001486436269047</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.5468778088281</v>
+        <v>6.560058818123338</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.853399290167161</v>
+        <v>7.866598029121924</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.174214276079404</v>
+        <v>7.187619403732235</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.336982319283194</v>
+        <v>8.350439612993412</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>9.567946673209818</v>
+        <v>9.581398961929928</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.318632233205086</v>
+        <v>9.332188279556689</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.739293736421544</v>
+        <v>9.728864100723392</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>444</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.686741859970205</v>
+        <v>2.699264149645828</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.310930171039992</v>
+        <v>6.323937302457594</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.765507627971807</v>
+        <v>5.778486770370272</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.353212539025762</v>
+        <v>6.366323343400701</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.326330152417107</v>
+        <v>7.339373048711472</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.241596435144828</v>
+        <v>7.254662689445304</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.350989612939898</v>
+        <v>8.364170622235136</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.416115852883728</v>
+        <v>9.429314591838491</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.34076544263057</v>
+        <v>8.354170570283401</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.487363469664359</v>
+        <v>9.500820763374577</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>11.09832320358636</v>
+        <v>11.11177549230647</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.12851904309191</v>
+        <v>11.14207508944351</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>11.82869082581864</v>
+        <v>11.81826119012049</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>303</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.962007224344482</v>
+        <v>1.974529514020105</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.3306316311822</v>
+        <v>2.343541440758251</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.58592794108727</v>
+        <v>3.598935072504872</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.386148070394434</v>
+        <v>3.399127212792898</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.827924875124246</v>
+        <v>4.841035679499186</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.795333809539571</v>
+        <v>4.808376705833936</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.040633095567628</v>
+        <v>5.053699349868104</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.55364771658811</v>
+        <v>6.566828725883347</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.82268083370613</v>
+        <v>6.835879572660893</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3.992357628876235</v>
+        <v>4.005762756529066</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.767802324360623</v>
+        <v>5.781259618070841</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.46225148830672</v>
+        <v>6.47570377702683</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.041996877361818</v>
+        <v>6.055552923713421</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.63165220303744</v>
+        <v>5.621222567339288</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>178</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.000943702261935</v>
+        <v>2.013465991937558</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>6.569145370196559</v>
+        <v>6.58205517977261</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.612478910790976</v>
+        <v>5.625486042208578</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6.304529796207468</v>
+        <v>6.317508938605933</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.451501839562255</v>
+        <v>7.464612643937194</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>6.06355051885096</v>
+        <v>6.076593415145325</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.102412307196651</v>
+        <v>7.115478561497127</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.320622166842121</v>
+        <v>8.333803176137359</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8.259622280659819</v>
+        <v>8.272821019614582</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.724103837204922</v>
+        <v>5.737508964857753</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.328339276932297</v>
+        <v>8.341796570642515</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>9.486317939895699</v>
+        <v>9.499770228615809</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>9.066063328950797</v>
+        <v>9.0796193753024</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.192189155609114</v>
+        <v>8.181759519910962</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>5.83989501312336</v>
+        <v>5.852417302798983</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>10.18070235254006</v>
+        <v>10.19361216211611</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8.595357455467273</v>
+        <v>8.608364586884875</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>8.725610588074773</v>
+        <v>8.738589730473237</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>12.94909413490737</v>
+        <v>12.96220493928231</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>8.484631310718264</v>
+        <v>8.497674207012629</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>7.209421402969795</v>
+        <v>7.222487657270271</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>9.123190385140681</v>
+        <v>9.136371394435919</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.871714308482183</v>
+        <v>7.884913047436946</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>4.640636742501869</v>
+        <v>4.6540418701547</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4.435883418184289</v>
+        <v>4.449340711894507</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3.279790385053538</v>
+        <v>3.293242673773648</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1.669059583632446</v>
+        <v>1.682615629984049</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.4621714650436459</v>
+        <v>-0.4726011007417981</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Days Since Halving is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Days Since Halving is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,157 +3904,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 27.82</t>
+          <t>X &lt; 27.84</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.302962129733785</v>
+        <v>-1.290439840058163</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.118928258818435</v>
+        <v>-2.105921127400833</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.717572531759302</v>
+        <v>-3.704461727384363</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1512979773849352</v>
+        <v>0.1643408736793006</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-5.8858166922683</v>
+        <v>-5.872750437967824</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.972047710097421</v>
+        <v>-3.958866700802183</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-12.36638092961306</v>
+        <v>-12.35318219065829</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-10.8355537336886</v>
+        <v>-10.82214860603577</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-13.42125943895856</v>
+        <v>-13.40780214524835</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-13.38687628161313</v>
+        <v>-13.37342399289302</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-11.42617851160565</v>
+        <v>-11.41262246525405</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.985980988853171</v>
+        <v>-9.996410624551324</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 74.38</t>
+          <t>X &lt; 74.4</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>225</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.937882764654418</v>
+        <v>-4.925360474978795</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.549456377618675</v>
+        <v>-2.536546568042624</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-7.388769528659715</v>
+        <v>-7.375762397242113</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-11.70296084049665</v>
+        <v>-11.68998169809819</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10.90804872223549</v>
+        <v>-10.89493791786055</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-11.94394011785316</v>
+        <v>-11.93089722155879</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-13.36200716845877</v>
+        <v>-13.3489409141583</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-12.49585723390694</v>
+        <v>-12.4826762246117</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-15.22352378675591</v>
+        <v>-15.21032504780115</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-13.85142674956162</v>
+        <v>-13.83802162190879</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-13.61173562943475</v>
+        <v>-13.59827833572453</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-14.91068580542265</v>
+        <v>-14.89723351670254</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-12.66427374970089</v>
+        <v>-12.65071770334929</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-8.414552417424602</v>
+        <v>-8.424982053122754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 120.9</t>
+          <t>X &lt; 121</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>363</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.529250992386281</v>
+        <v>-1.516728702710658</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.6614857623753352</v>
+        <v>-0.648575952799284</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.260211218283224</v>
+        <v>-3.247204086865622</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.507368553995278</v>
+        <v>-4.494389411596813</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.464522551436595</v>
+        <v>-1.451411747061655</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.370937363032233</v>
+        <v>-3.357894466737868</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.455671080304512</v>
+        <v>-3.442604826004036</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.371890291758184</v>
+        <v>-3.358709282462947</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.085782739923964</v>
+        <v>-5.072584000969201</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.181086988312764</v>
+        <v>-3.167681860659933</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.936804499958171</v>
+        <v>-3.923347206247954</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.453385529940562</v>
+        <v>-4.439933241220452</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-3.771711766229814</v>
+        <v>-3.758155719878211</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.144579965633966</v>
+        <v>-2.155009601332118</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>504</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.474815648043993</v>
+        <v>1.487337937719616</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.04578171761942</v>
+        <v>2.058691527195471</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.857262217372039</v>
+        <v>0.8702693487896411</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1938645563287338</v>
+        <v>0.206843698727198</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.631633817447046</v>
+        <v>2.644744621821985</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.9449487710357261</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.455453149001542</v>
+        <v>1.468519403302018</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.385095147045433</v>
+        <v>1.398276156340671</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.9272698640377399</v>
+        <v>0.9404686029925031</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.656509758374895</v>
+        <v>2.669914886027726</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.054931037231917</v>
+        <v>2.068388330942135</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.692488797751956</v>
+        <v>1.705941086472066</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.859535774108636</v>
+        <v>2.873091820460239</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.696558693686512</v>
+        <v>4.68612905798836</v>
       </c>
     </row>
     <row r="10">
@@ -4119,98 +4119,98 @@
         <v>645</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.855398889092349</v>
+        <v>2.867921178767972</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.414367911787004</v>
+        <v>3.427277721363055</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.484615484260182</v>
+        <v>3.497622615677784</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.614868616867682</v>
+        <v>3.627847759266146</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>5.105062082139447</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.304121897650717</v>
+        <v>4.317164793945082</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.684504459448206</v>
+        <v>4.697570713748682</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.992514859116319</v>
+        <v>5.005695868411557</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.086553732623933</v>
+        <v>5.099752471578697</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.872087462324686</v>
+        <v>6.885492589977517</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.44252793645672</v>
+        <v>7.455985230166938</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7.786988613182004</v>
+        <v>7.800440901902114</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>9.227199118516161</v>
+        <v>9.240755164867764</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>10.56219176862191</v>
+        <v>10.55176213292376</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 260.6</t>
+          <t>X &lt; 260.7</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>783</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.828400760249792</v>
+        <v>3.840923049925415</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.132535959546075</v>
+        <v>4.145445769122126</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.993095094584227</v>
+        <v>4.006102226001829</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.378776068826461</v>
+        <v>4.391755211224925</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.628349745197461</v>
+        <v>5.6414605495724</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.648652474739421</v>
+        <v>4.661695371033787</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.563918757467142</v>
+        <v>4.576985011767619</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.863018883589866</v>
+        <v>4.876199892885104</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.54659115577283</v>
+        <v>4.559789894727594</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.86760262464017</v>
+        <v>5.881007752293002</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.556846746044172</v>
+        <v>6.57030403975439</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.974371665841716</v>
+        <v>6.987823954561826</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8.469825867157347</v>
+        <v>8.48338191350895</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>10.1244003284247</v>
+        <v>10.11397069272655</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>924</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.675392848621193</v>
+        <v>3.687915138296816</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.202347374185074</v>
+        <v>5.215257183761125</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.132153992263817</v>
+        <v>5.145161123681419</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.019982882447074</v>
+        <v>6.032962024845538</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.563812749625974</v>
+        <v>6.576923554000913</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6.320129146216104</v>
+        <v>6.333172042510469</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.343620537168924</v>
+        <v>6.3566867914694</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6.742238004188295</v>
+        <v>6.755419013483532</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.923662360430235</v>
+        <v>5.936861099384998</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>7.021589123454255</v>
+        <v>7.034994251107086</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>7.466186448487328</v>
+        <v>7.479643742197545</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>7.608794714057865</v>
+        <v>7.622247002777975</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>8.487241401814266</v>
+        <v>8.500797448165869</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>9.710988708116517</v>
+        <v>9.700559072418365</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>1062</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.074639525021205</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.463726296580944</v>
+        <v>4.476636106156995</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.822153258534257</v>
+        <v>4.835160389951859</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.329054225416719</v>
+        <v>5.342033367815183</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.826414554600667</v>
+        <v>5.839525358975607</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.464722782335166</v>
+        <v>5.477765678629531</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.191665147925406</v>
+        <v>5.204731402225882</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.571939376262549</v>
+        <v>5.585120385557786</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.134291655805292</v>
+        <v>5.147490394760055</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.073243683583399</v>
+        <v>6.08664881123623</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.527624069246983</v>
+        <v>6.5410813629572</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.467845268023673</v>
+        <v>6.481297556743783</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>7.27169611847237</v>
+        <v>7.285252164823973</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>7.709741367886139</v>
+        <v>7.699311732187986</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>1203</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.951283209299582</v>
+        <v>2.963805498975205</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.165977260508235</v>
+        <v>4.178887070084286</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.519238229722113</v>
+        <v>4.532245361139715</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.981993440467598</v>
+        <v>4.994972582866062</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.189208135619872</v>
+        <v>6.202318939994811</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.406018319387066</v>
+        <v>5.419061215681431</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.73691219978727</v>
+        <v>5.749978454087746</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.435979840074772</v>
+        <v>5.44916084937001</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.042477875754479</v>
+        <v>5.055676614709242</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.688612042347501</v>
+        <v>5.702017170000332</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>6.315113913374887</v>
+        <v>6.328571207085105</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>6.432622590254816</v>
+        <v>6.446074878974926</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>7.00987421372389</v>
+        <v>7.023430260075493</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.425846585069159</v>
+        <v>7.415416949371007</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>1341</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.54011872676989</v>
+        <v>2.552641016445513</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.46396644117327</v>
+        <v>3.476876250749321</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.665667458663187</v>
+        <v>3.678674590080789</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.467061530868001</v>
+        <v>4.480040673266465</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5.270922194990455</v>
+        <v>5.284032999365394</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.748080762087184</v>
+        <v>4.76112365838155</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.259916768901398</v>
+        <v>5.272983023201874</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>5.240160663184781</v>
+        <v>5.253341672480019</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.477445639045733</v>
+        <v>5.490644378000496</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>6.118744764234052</v>
+        <v>6.132149891886883</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>6.585132379513801</v>
+        <v>6.598589673224019</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.843229183391664</v>
+        <v>6.856681472111774</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.317829158576515</v>
+        <v>7.331385204928118</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7.716692921874426</v>
+        <v>7.706263286176274</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>1482</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.364861274931727</v>
+        <v>2.377383564607349</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.114961076272458</v>
+        <v>3.127870885848509</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.664761735397875</v>
+        <v>3.677768866815477</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.334825934132226</v>
+        <v>4.34780507653069</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.876026851313767</v>
+        <v>4.889137655688707</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.633657722902576</v>
+        <v>4.646700619196942</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.156211455023012</v>
+        <v>5.169277709323488</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>5.161362739102508</v>
+        <v>5.174543748397745</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.302792002717773</v>
+        <v>5.315990741672536</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.464812566677701</v>
+        <v>5.478217694330532</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>5.799870308486973</v>
+        <v>5.813327602197191</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.3065881486934</v>
+        <v>6.32004043741351</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.763526520204643</v>
+        <v>6.777082566556246</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>7.148200619012648</v>
+        <v>7.137770983314496</v>
       </c>
     </row>
     <row r="17">
@@ -4483,46 +4483,46 @@
         <v>1623</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.589740977387066</v>
+        <v>2.602263267062689</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.381124850559587</v>
+        <v>3.394034660135638</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.033699150740581</v>
+        <v>4.046706282158183</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4.841709523027681</v>
+        <v>4.854688665426146</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.412345609249414</v>
+        <v>5.425456413624353</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5.155258896318131</v>
+        <v>5.168301792612496</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>5.686668124209113</v>
+        <v>5.699734378509589</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5.589170492525589</v>
+        <v>5.602351501820827</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.713013489892269</v>
+        <v>5.726212228847032</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>5.910331311641912</v>
+        <v>5.923736439294743</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.136878048938627</v>
+        <v>6.150335342648845</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>6.664175562414684</v>
+        <v>6.677627851134794</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.168135369214703</v>
+        <v>7.181691415566306</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>7.479470996007308</v>
+        <v>7.469041360309156</v>
       </c>
     </row>
     <row r="18">
@@ -4535,46 +4535,46 @@
         <v>1761</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.964256171556066</v>
+        <v>1.976778461231689</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.113045988461202</v>
+        <v>2.125955798037253</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.740323789530713</v>
+        <v>2.753330920948315</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.211292424693575</v>
+        <v>3.224271567092039</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.524659966009821</v>
+        <v>3.537770770384761</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.140670898614751</v>
+        <v>3.153713794909116</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.510224518082964</v>
+        <v>3.52329077238344</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.213398870579148</v>
+        <v>3.226579879874386</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.982041233119162</v>
+        <v>2.995239972073925</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.267634389942451</v>
+        <v>3.281039517595282</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.290024733995118</v>
+        <v>3.303482027705336</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>4.176196647728965</v>
+        <v>4.189648936449075</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.38058712480224</v>
+        <v>4.394143171153843</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4.573522539985966</v>
+        <v>4.563092904287814</v>
       </c>
     </row>
     <row r="19">
@@ -4587,46 +4587,46 @@
         <v>1902</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.712660523112838</v>
+        <v>1.725182812788461</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.573221505311572</v>
+        <v>1.586131314887623</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.229877509545688</v>
+        <v>2.24288464096329</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.307554406611651</v>
+        <v>2.320533549010115</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.505200489120973</v>
+        <v>2.518311293495913</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.961422658172076</v>
+        <v>1.974465554466441</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.402451296315142</v>
+        <v>2.415517550615618</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.935267897533642</v>
+        <v>1.94844890682888</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.611386833643671</v>
+        <v>1.624585572598434</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.760210123904905</v>
+        <v>1.773615251557736</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.870914212836546</v>
+        <v>1.884371506546763</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.378483490055793</v>
+        <v>2.391935778775903</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.431414998984707</v>
+        <v>2.44497104533631</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.523407624636384</v>
+        <v>2.512977988938232</v>
       </c>
     </row>
     <row r="20">
@@ -4639,46 +4639,46 @@
         <v>2040</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.084993052339044</v>
+        <v>1.097515342014667</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9440076746689101</v>
+        <v>0.9569174842449613</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.578550732778197</v>
+        <v>1.591557864195799</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.757823473228832</v>
+        <v>1.770802615627296</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.660578728744902</v>
+        <v>1.673689533119841</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.222726548813505</v>
+        <v>1.23576944510787</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.628188909972593</v>
+        <v>1.641255164273069</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.161005511191092</v>
+        <v>1.17418652048633</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.9529468014793849</v>
+        <v>0.9661455404341481</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.9361549497847861</v>
+        <v>0.9495600774376172</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.025519272526026</v>
+        <v>1.038976566236244</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.501078900459696</v>
+        <v>1.514531189179806</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.522000760103033</v>
+        <v>1.535556806454636</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.428584837477366</v>
+        <v>1.418155201779214</v>
       </c>
     </row>
     <row r="21">
@@ -4691,46 +4691,46 @@
         <v>2181</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.059977544072467</v>
+        <v>1.07249983374809</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.7322186949779876</v>
+        <v>0.7451285045540388</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.162659479440549</v>
+        <v>1.175666610858151</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.33876313932911</v>
+        <v>1.351742281727574</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.212996669786513</v>
+        <v>1.226107474161452</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5475775345998457</v>
+        <v>0.5606204308942111</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8296480355760707</v>
+        <v>0.8427142898765467</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.2249130549513794</v>
+        <v>0.2380940642466172</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.06533946763623533</v>
+        <v>-0.05214072868147213</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1818562161671551</v>
+        <v>-0.168451088514324</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.1115063767983457</v>
+        <v>-0.09804908308812799</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.1521294169524054</v>
+        <v>0.1655817056725155</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.1903800788181442</v>
+        <v>0.2039361251697471</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.07329719284591363</v>
+        <v>0.06286755714776149</v>
       </c>
     </row>
     <row r="22">
@@ -4743,46 +4743,46 @@
         <v>2328</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9000324701680285</v>
+        <v>0.9125547598436512</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.1101665723494918</v>
+        <v>-0.09725676277344064</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5258925561054681</v>
+        <v>0.5388996875230703</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.656145688712968</v>
+        <v>0.6691248311114322</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.5043224117851324</v>
+        <v>0.5174332161600717</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1432528326297984</v>
+        <v>-0.130209936335433</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.1420758969811189</v>
+        <v>-0.1290096426806429</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.5663039693021403</v>
+        <v>-0.5531229600069025</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.056857120089248</v>
+        <v>-1.043658381134485</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.004920449447063</v>
+        <v>-0.9915153217942319</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.9948971414622392</v>
+        <v>-0.9814398477520214</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.8316480047353636</v>
+        <v>-0.8181957160152535</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.9082600039964177</v>
+        <v>-0.8947039576448148</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.045136609864464</v>
+        <v>-1.055566245562616</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3178066597097029</v>
+        <v>0.3091281284379548</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.3484832067780843</v>
+        <v>-0.3571623645620292</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.564428041901202</v>
+        <v>0.5553121083603116</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.7570311176858908</v>
+        <v>0.747853242952182</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4016857910388438</v>
+        <v>0.3925570560035396</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.07752198811598277</v>
+        <v>0.06856644162167669</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1059685211157841</v>
+        <v>-0.1148698209322845</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.1887019110448165</v>
+        <v>-0.1976520700223361</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5095834160871036</v>
+        <v>-0.5184200941160952</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3299972184585656</v>
+        <v>-0.3390512575073146</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2703377799723867</v>
+        <v>-0.2794552805048625</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2133616155611477</v>
+        <v>-0.2225023339068457</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3688742339623943</v>
+        <v>-0.3780271023004715</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.419396987469014</v>
+        <v>-0.4120684130904735</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.09408070566522042</v>
+        <v>0.08660013530816713</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.850348819356185</v>
+        <v>-0.8577033412542008</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2729194821165919</v>
+        <v>-0.2805545133018228</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3124846500204654</v>
+        <v>-0.3200908628608232</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7159755515037887</v>
+        <v>-0.7235093464319817</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.084110406326921</v>
+        <v>-1.091466327249861</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.300985047940095</v>
+        <v>-1.308275009977343</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.404416308051665</v>
+        <v>-1.411738009508731</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.826577221870416</v>
+        <v>-1.833751221017479</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.73993381332641</v>
+        <v>-1.747266744894375</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.809341944688128</v>
+        <v>-1.816682306705822</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.906992008454111</v>
+        <v>-1.914294886705093</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.19179668548071</v>
+        <v>-2.199055494713441</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.303653755856729</v>
+        <v>-2.296541686150277</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2756</v>
+        <v>2757</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1279634195238017</v>
+        <v>-0.1343456334224413</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.034202684619316</v>
+        <v>-1.040458931109917</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6148065523114852</v>
+        <v>-0.6212665719370349</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5373787725284771</v>
+        <v>-0.5438547254442909</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9839980893241034</v>
+        <v>-0.9903826033269354</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.318276827935172</v>
+        <v>-1.324507830359281</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.311337606388562</v>
+        <v>-1.317585390762254</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.505753444382449</v>
+        <v>-1.511992185523759</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.94572588744407</v>
+        <v>-1.951816720502087</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.979446073233113</v>
+        <v>-1.985633195815183</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.092102912266697</v>
+        <v>-2.098278335724537</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.328138065514509</v>
+        <v>-2.334227596683213</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.801379299211227</v>
+        <v>-2.807352946278939</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.858674333244629</v>
+        <v>-2.852258077787241</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1910328219281823</v>
+        <v>-0.1964776931932306</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.028353287591557</v>
+        <v>-1.033682879611924</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.7859879300046586</v>
+        <v>-0.7914455262287774</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7404565405310564</v>
+        <v>-0.7459193413810823</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.9851306217537257</v>
+        <v>-0.9905691528106715</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.426441552161826</v>
+        <v>-1.43170015801212</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.389555377825168</v>
+        <v>-1.394838791381481</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.493905230232585</v>
+        <v>-1.499205150231539</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.846542394612563</v>
+        <v>-1.851730490446684</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.850967137933445</v>
+        <v>-1.856246600850511</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.899091951273824</v>
+        <v>-1.904379680088546</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.052918759314807</v>
+        <v>-2.058153056932433</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.281941106498678</v>
+        <v>-2.287144057264427</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.25507709812878</v>
+        <v>-2.249688747394664</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3035</v>
+        <v>3036</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1640419947506544</v>
+        <v>-0.1686825113477255</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.7082282114807654</v>
+        <v>-0.7128370317346651</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6916074946624775</v>
+        <v>-0.6962597899416707</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4780018913997708</v>
+        <v>-0.4827153378443043</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.7359068037072447</v>
+        <v>-0.7405865221298455</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.077908789120549</v>
+        <v>-1.082452193087491</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.9149328752306332</v>
+        <v>-0.9195401035547235</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9040562912345749</v>
+        <v>-0.9087117275702852</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.144576418334864</v>
+        <v>-1.149160957041531</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.022645352172127</v>
+        <v>-1.027349107288899</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.110528695048089</v>
+        <v>-1.11522469966004</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.156761977083292</v>
+        <v>-1.161442426072746</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.361243446670592</v>
+        <v>-1.365897156757256</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.32394286223515</v>
+        <v>-1.31958020859048</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3176</v>
+        <v>3177</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.03086396890887499</v>
+        <v>0.02692096006126121</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1213231000500201</v>
+        <v>-0.1253413835542716</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2168558515687522</v>
+        <v>-0.2208760177635085</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1501465041361172</v>
+        <v>0.1460187202680814</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.05718529994349808</v>
+        <v>-0.06129071133199204</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.3706570357761123</v>
+        <v>-0.3746439510198201</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.1870150226843563</v>
+        <v>-0.1910682173408844</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.2599469049733614</v>
+        <v>-0.2640145846494093</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3665605676424235</v>
+        <v>-0.370601603426536</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1302527453687432</v>
+        <v>-0.1344343502611594</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1286696757805572</v>
+        <v>-0.1328695306930854</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1395509197503202</v>
+        <v>-0.1437470953960513</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.2903360726470723</v>
+        <v>-0.2945188361372075</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.2117816365681762</v>
+        <v>-0.2084255532801365</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3314</v>
+        <v>3315</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.04638734856069249</v>
+        <v>0.0431224310041074</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.04608228795475355</v>
+        <v>-0.04942102951943639</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.1540159781166892</v>
+        <v>-0.1573485534524437</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.173092107758464</v>
+        <v>0.1696674247088339</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.07239063978678217</v>
+        <v>0.06896099910696307</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1554592830147143</v>
+        <v>-0.1588037317403632</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.07323872521879338</v>
+        <v>-0.07661500607080285</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2528853463567415</v>
+        <v>-0.2562384046779513</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3274707587354229</v>
+        <v>-0.3308069755119902</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.01435585039819642</v>
+        <v>0.01086191061440189</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.113192769420678</v>
+        <v>-0.1166629047420216</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.1824992352577937</v>
+        <v>-0.1859482187425385</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.3143491644821879</v>
+        <v>-0.3177864608884917</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.138149279223029</v>
+        <v>-0.1353892929417597</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3455</v>
+        <v>3456</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.01362286461597506</v>
+        <v>-0.01622880078514299</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.02367360032162225</v>
+        <v>-0.02635817896150172</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3740872179589374</v>
+        <v>-0.3766917950564164</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.02619316372898339</v>
+        <v>-0.02889302719993481</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1159009162308706</v>
+        <v>-0.1186031415257744</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2935406568848364</v>
+        <v>-0.2961782069321615</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2470447190075902</v>
+        <v>-0.2497013338329594</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2939887951127602</v>
+        <v>-0.29665658278617</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.512541127796375</v>
+        <v>-0.5151502428314885</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.2193558234750768</v>
+        <v>-0.2220935551136662</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.3501200520297019</v>
+        <v>-0.3528316748398836</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5598999602775336</v>
+        <v>-0.5625506557038946</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6746904163675538</v>
+        <v>-0.6773303732943319</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6403121858761267</v>
+        <v>-0.6379450160857161</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3593</v>
+        <v>3594</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3303767561500734</v>
+        <v>-0.3323160859821002</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.4850396724252732</v>
+        <v>-0.4869995168316876</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.7540426819461814</v>
+        <v>-0.7559442434433734</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5811179318094517</v>
+        <v>-0.5830634591044799</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6881708765941852</v>
+        <v>-0.6901086089513129</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.8477631299794268</v>
+        <v>-0.8496460647940438</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.9731182795698814</v>
+        <v>-0.9749707206935199</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.064163244835903</v>
+        <v>-1.066009557945037</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.27688676618893</v>
+        <v>-1.278677367890062</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.166782138311504</v>
+        <v>-1.168637396104323</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.356266589761042</v>
+        <v>-1.358078168918865</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.556953770188535</v>
+        <v>-1.558709230458568</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.516805747474962</v>
+        <v>-1.51858974785555</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.585718573839856</v>
+        <v>-1.583579715894039</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3734</v>
+        <v>3735</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3183649281630068</v>
+        <v>-0.3197634158064986</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.5011678328004976</v>
+        <v>-0.5025638262936738</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.7482117479150148</v>
+        <v>-0.7495537005582378</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6837300712658916</v>
+        <v>-0.6850862819878216</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7536271352731632</v>
+        <v>-0.7549806529032921</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.8692919796026715</v>
+        <v>-0.8706069018509055</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.8594677404983386</v>
+        <v>-0.8607884110405308</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.9914009059212034</v>
+        <v>-0.9927002823502775</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.11814801783374</v>
+        <v>-1.119415956892063</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.9907169225596562</v>
+        <v>-0.9920437906407713</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.12721150134626</v>
+        <v>-1.128508405280449</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.318965605565403</v>
+        <v>-1.320210949580968</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.322908287853501</v>
+        <v>-1.324165240822516</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.406518137831668</v>
+        <v>-1.404901731837619</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3875</v>
+        <v>3876</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1529033407861036</v>
+        <v>-0.1538396612877548</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1816777422815079</v>
+        <v>-0.1826371030220528</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2796027190296968</v>
+        <v>-0.2805447200846345</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2640934016292178</v>
+        <v>-0.265037453802428</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3766378056546458</v>
+        <v>-0.3775634004860322</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3741916415891069</v>
+        <v>-0.3751128068660421</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3934342678920544</v>
+        <v>-0.3943525374736083</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5116607209807214</v>
+        <v>-0.5125577289908918</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.5328021372713678</v>
+        <v>-0.5336953131966595</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.3118546949083552</v>
+        <v>-0.3128211637186382</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4506560351421669</v>
+        <v>-0.4515910451857295</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.5050457056891773</v>
+        <v>-0.505966540598024</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4723232853045971</v>
+        <v>-0.4732609068571563</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.4403588690375031</v>
+        <v>-0.4394299375396855</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4000</v>
+        <v>4001</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.08875354572703742</v>
+        <v>-0.08928673307545409</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2914526111403362</v>
+        <v>-0.2919526095189369</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2490703680181383</v>
+        <v>-0.2495853727600021</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2798519460660671</v>
+        <v>-0.2803581628202068</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3308474251539266</v>
+        <v>-0.3313468954166581</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2692894192503701</v>
+        <v>-0.2698013539276332</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3155052135465368</v>
+        <v>-0.3160067824217734</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.3697131167493453</v>
+        <v>-0.3702063801728102</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3670943235848725</v>
+        <v>-0.367589151645376</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2544681526030246</v>
+        <v>-0.2550003984381206</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3703333478126396</v>
+        <v>-0.3708391082853097</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4219301832337479</v>
+        <v>-0.4224229579549359</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.4033389833924659</v>
+        <v>-0.4038411416301457</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3645524174246049</v>
+        <v>-0.3639972993112082</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1194427029711207</v>
+        <v>-0.1196696819462346</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2082754499789061</v>
+        <v>-0.2084887805253786</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1758855118780147</v>
+        <v>-0.1761087738183988</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1785943687617646</v>
+        <v>-0.1788164524627902</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2651045350553858</v>
+        <v>-0.2653082882309263</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.173746716260446</v>
+        <v>-0.1739713949278752</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1476692021090997</v>
+        <v>-0.1479007711386373</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1869141444760416</v>
+        <v>-0.1871385508735983</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1613134915619625</v>
+        <v>-0.1615445599962655</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.09512286148613214</v>
+        <v>-0.09537436376994179</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.09094806129546384</v>
+        <v>-0.09120171298172863</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.0672613262559878</v>
+        <v>-0.06752071872028154</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.03423711966426168</v>
+        <v>-0.03450676584928658</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.009482755999925985</v>
+        <v>0.009694381553678966</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/cycle/days_since_halving.xlsx
+++ b/workspaces/btc_daily_14days/cycle/days_since_halving.xlsx
@@ -568,365 +568,365 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 51.12</t>
+          <t>X ≈ 51.27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.067521686637434</v>
+        <v>-7.55774164285944</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.554741895792937</v>
+        <v>-7.693556148319878</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-10.48595060671041</v>
+        <v>-10.9782147836324</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-16.0180395826967</v>
+        <v>-16.63383000017856</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-15.14398290538354</v>
+        <v>-15.68021535609657</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-19.09793754991691</v>
+        <v>-19.02794477362578</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-17.77116736963619</v>
+        <v>-17.64634950435594</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-17.53396044064589</v>
+        <v>-17.39247191666301</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-16.89077356833307</v>
+        <v>-16.70986240775653</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-15.61868718129386</v>
+        <v>-15.36544736949172</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-13.70114958277118</v>
+        <v>-13.40105565300835</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-15.7969059019446</v>
+        <v>-15.51918683954393</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-13.38486201846672</v>
+        <v>-13.02042102987904</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.488811840356796</v>
+        <v>-6.977620974715506</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 97.7</t>
+          <t>X ≈ 97.82</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.028052384440585</v>
+        <v>4.214103321554553</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.422471699379251</v>
+        <v>3.343478057672179</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.475329510005473</v>
+        <v>4.366860432023621</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.220372042243895</v>
+        <v>8.034923284497161</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.91428395737535</v>
+        <v>14.62418058801023</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.59902767192709</v>
+        <v>10.65374301081371</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12.68714798858511</v>
+        <v>13.42764314971794</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.50035661556411</v>
+        <v>12.25766382784949</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>11.44248150330442</v>
+        <v>11.51566336112106</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>14.2155348275973</v>
+        <v>14.23779103419299</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.84229491991233</v>
+        <v>11.91132523356382</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>12.60385114020935</v>
+        <v>12.6812617979683</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.73796131380999</v>
+        <v>10.87120095996827</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.067771570065979</v>
+        <v>8.286023798642823</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 144.2</t>
+          <t>X ≈ 144.4</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.189214210626318</v>
+        <v>9.052640467491855</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8.999280671783012</v>
+        <v>8.198942799728883</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.43726124062129</v>
+        <v>10.69924606717186</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12.27776971732909</v>
+        <v>11.55459654918717</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>13.15828142934188</v>
+        <v>12.51459392871988</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>12.04357934933419</v>
+        <v>12.06753401864076</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>14.08584444397165</v>
+        <v>13.45666757585134</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>13.62326210281754</v>
+        <v>12.99514677818777</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>16.39922440515896</v>
+        <v>16.58020236999031</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>17.67970581974819</v>
+        <v>17.93299294933888</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>17.47995531766774</v>
+        <v>17.73386155943571</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>17.51899398290619</v>
+        <v>17.79673456106382</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>19.93969846196337</v>
+        <v>20.30414836549999</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>22.2984222021964</v>
+        <v>22.73252395282072</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 190.8</t>
+          <t>X ≈ 190.9</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>141</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.77342925730273</v>
+        <v>7.744447596323269</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.290139941262488</v>
+        <v>8.289050536745243</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.84864966280988</v>
+        <v>12.84862276572458</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15.81129702905745</v>
+        <v>15.81094303946452</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>13.86316171007415</v>
+        <v>13.91168277855594</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>16.28725531357321</v>
+        <v>16.31126736564292</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>16.20721083966824</v>
+        <v>16.25521681789708</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>17.86963850978749</v>
+        <v>17.91888745316167</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>19.93858802181627</v>
+        <v>20.01181637917814</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>21.92870629390163</v>
+        <v>22.02800579484364</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>26.69088000346494</v>
+        <v>26.79076372852091</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>29.56817011220149</v>
+        <v>29.69184015235145</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>31.99260029984633</v>
+        <v>32.14127094386613</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>31.51828035822445</v>
+        <v>31.69027911779143</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 237.4</t>
+          <t>X ≈ 237.5</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>138</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8.354670859555</v>
+        <v>8.325721577406462</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.473489839124859</v>
+        <v>7.472406790229314</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>6.360029605366535</v>
+        <v>6.359956066319782</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.936876735444599</v>
+        <v>7.936471427253686</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.124545861010212</v>
+        <v>8.173025510595131</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.25541341087655</v>
+        <v>6.279363641505441</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.003362250066616</v>
+        <v>4.051295314972776</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.261805867287151</v>
+        <v>4.310985555893453</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.031692007090463</v>
+        <v>2.104840535775381</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.183260729522281</v>
+        <v>1.28248420430532</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.427361747684436</v>
+        <v>2.527180409551093</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.187008115367711</v>
+        <v>3.310630318351613</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.94153360156659</v>
+        <v>5.090179417667464</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.067771570065823</v>
+        <v>8.239770329632314</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 283.9</t>
+          <t>X ≈ 284.1</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>141</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.823433115156945</v>
+        <v>2.794440470093051</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.11164895682533</v>
+        <v>11.11062797536416</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>11.42883911307357</v>
+        <v>11.42883639225479</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>15.09741377907556</v>
+        <v>15.09709721802275</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11.73569285867912</v>
+        <v>11.78420730707573</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>15.57428879539336</v>
+        <v>15.59832014274825</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>16.2026024799861</v>
+        <v>16.25061989997886</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>17.15738736443431</v>
+        <v>17.20664381318372</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>13.56155673746878</v>
+        <v>13.63475682150882</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>13.42514004129531</v>
+        <v>13.52440438318544</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>12.5164503651055</v>
+        <v>12.61629365363405</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>11.13748699342091</v>
+        <v>11.26112006943826</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8.594268182032565</v>
+        <v>8.74291460512655</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.404805180919638</v>
+        <v>7.576803940486464</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 330.5</t>
+          <t>X ≈ 330.6</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>138</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.031686715909366</v>
+        <v>-1.060712984825706</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.4727722356001465</v>
+        <v>-0.4739207747940597</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.744680219663692</v>
+        <v>2.744596585995204</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.7080662735292975</v>
+        <v>0.7076192343879768</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.894205719858121</v>
+        <v>0.9426189124770303</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2536895661163925</v>
+        <v>-0.2297812888459489</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.506775326127531</v>
+        <v>-2.458893167023504</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.250145378551295</v>
+        <v>-2.201008675626213</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1403354251146496</v>
+        <v>-0.06721053532862697</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2653614748109021</v>
+        <v>-0.1661605195234728</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2545075004265982</v>
+        <v>0.3543076234313602</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.158747072226838</v>
+        <v>-1.035144924216013</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.8541161810178295</v>
+        <v>-0.7054832396447068</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.700344371963496</v>
+        <v>-5.5283456123965</v>
       </c>
     </row>
     <row r="13">
@@ -939,98 +939,98 @@
         <v>141</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.115216131398348</v>
+        <v>2.086256048198742</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.922388510651409</v>
+        <v>1.9212802805759</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.236381189922938</v>
+        <v>2.236302253251097</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.366890670265754</v>
+        <v>2.366471173605298</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>8.901928556053775</v>
+        <v>8.950421041582558</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.95857050228291</v>
+        <v>4.982527024457937</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>9.829450737875746</v>
+        <v>9.877426888891378</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.412400066999112</v>
+        <v>4.461575580907372</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.35388616522031</v>
+        <v>4.427027338634538</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.798459225542459</v>
+        <v>2.897662437472171</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.720959328469895</v>
+        <v>4.82076673493377</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.17514761063299</v>
+        <v>6.298759300886744</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.048879627592662</v>
+        <v>5.197514758132435</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.277145606451882</v>
+        <v>5.44914436601821</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 423.6</t>
+          <t>X ≈ 423.7</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>138</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.03237579590062</v>
+        <v>-1.061363103510722</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.638783126787374</v>
+        <v>-2.639952602060802</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.754757465688577</v>
+        <v>-3.754913032777722</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.01585722447870808</v>
+        <v>-0.01629639150362294</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.720324989748356</v>
+        <v>-2.67196712116953</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.9777776462317362</v>
+        <v>-0.95387869992269</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.10637870890509</v>
+        <v>1.15427885079621</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.534189846763283</v>
+        <v>3.583355986195656</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>9.262515320958968</v>
+        <v>9.335682378732166</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>9.864637161469474</v>
+        <v>9.963867160437616</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.940294144742239</v>
+        <v>9.040111565198359</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>10.42691666759111</v>
+        <v>10.5505337437883</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>10.01142127621505</v>
+        <v>10.16005878869718</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>141</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.7014050364651183</v>
+        <v>0.6724731984033241</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1977918799039031</v>
+        <v>-0.1989173483638069</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.647217108687911</v>
+        <v>3.647180324179793</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.070952101915701</v>
+        <v>3.070567879645388</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.12138322453491</v>
+        <v>1.1697733922013</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.541305598316093</v>
+        <v>3.56525425479682</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.1657110794212</v>
+        <v>4.213635471636479</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.409804049456078</v>
+        <v>4.458974795295482</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.643367337377107</v>
+        <v>3.716491248799429</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.7442824162632675</v>
+        <v>-0.6451211117027498</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.656637735362921</v>
+        <v>-1.556872367858247</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.212941289528615</v>
+        <v>1.336526297989671</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.503469195390757</v>
+        <v>1.652090441266743</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.73104631567157</v>
+        <v>1.903045075238232</v>
       </c>
     </row>
     <row r="16">
@@ -1095,98 +1095,98 @@
         <v>141</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.934184439180299</v>
+        <v>4.90537755184782</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>6.154657148812475</v>
+        <v>6.153668600985853</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.881891553053386</v>
+        <v>7.881955612029031</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.13340062337782</v>
+        <v>10.13315545692102</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>11.01429783132281</v>
+        <v>11.06282537297559</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>10.60948842580164</v>
+        <v>10.63353871533042</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>11.23664023925669</v>
+        <v>11.28464596354959</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>10.06858902090922</v>
+        <v>10.11781536354713</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>10.0126117222424</v>
+        <v>10.08577976888538</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>10.5851536938178</v>
+        <v>10.68437195675214</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>9.677398203851666</v>
+        <v>9.777205620844384</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>10.42522695886617</v>
+        <v>10.54883213961606</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>11.42846102554351</v>
+        <v>11.57709227410204</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>10.95090447170011</v>
+        <v>11.1229032312666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 563.3</t>
+          <t>X ≈ 563.4</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>138</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-5.35949107472959</v>
+        <v>-5.388486338751754</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-12.73519779048718</v>
+        <v>-12.73656693166991</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-12.41305774569701</v>
+        <v>-12.41336289637849</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-15.89780245267819</v>
+        <v>-15.89847915424314</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-18.60657634105371</v>
+        <v>-18.55852324642813</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-20.48264948699676</v>
+        <v>-20.45903144390707</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-22.02027968395746</v>
+        <v>-21.97268931472439</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-24.66217035771293</v>
+        <v>-24.61331997191515</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-29.07075924626712</v>
+        <v>-28.99795346037866</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-27.75966524846795</v>
+        <v>-27.6607374779919</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-30.14542683474662</v>
+        <v>-30.04584655198008</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-25.05392810991368</v>
+        <v>-24.93046053353497</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-28.3799963704206</v>
+        <v>-28.23144324495787</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-29.61338785022437</v>
+        <v>-29.44138909065754</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>141</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.417170707753492</v>
+        <v>-1.4460457590178</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.136978987548133</v>
+        <v>-5.138209536361408</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.121993737930644</v>
+        <v>-4.122151945016732</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-8.937596021751212</v>
+        <v>-8.938179640234573</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-10.1839800592966</v>
+        <v>-10.13586053900729</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-12.71695556614164</v>
+        <v>-12.69328147314802</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-11.39270480017161</v>
+        <v>-11.34504035533675</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-13.98391955776896</v>
+        <v>-13.93501333511892</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-15.46483438112504</v>
+        <v>-15.39197110810042</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-17.02743037092996</v>
+        <v>-16.92848654045355</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-15.82173347096571</v>
+        <v>-15.72212164775156</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-20.04542507537625</v>
+        <v>-19.92197440712026</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-21.89073566926442</v>
+        <v>-21.74219127740104</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-23.09164871978926</v>
+        <v>-22.91964996022276</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>138</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-7.516406525818354</v>
+        <v>-7.54542866343904</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-7.679601125860721</v>
+        <v>-7.680922475313601</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-7.357177622843302</v>
+        <v>-7.35742795784396</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-5.787887266823773</v>
+        <v>-5.788426659202777</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-9.934417968887793</v>
+        <v>-9.886368208486758</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-8.918182246343591</v>
+        <v>-8.894496719878958</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-9.007206553431217</v>
+        <v>-8.959565275412956</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-9.475144115896768</v>
+        <v>-9.42623794895642</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.093122933918195</v>
+        <v>-8.020242118884205</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-10.39140329540356</v>
+        <v>-10.29246548815209</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-10.60010889250878</v>
+        <v>-10.50050981976146</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-10.57037599221681</v>
+        <v>-10.44692187977835</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-10.99435821437283</v>
+        <v>-10.84581207495376</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-13.67135886471712</v>
+        <v>-13.49936010515013</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>141</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6992542879539556</v>
+        <v>0.6705188297124849</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.310625518965757</v>
+        <v>-2.311817059509025</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.823243071444949</v>
+        <v>-4.82345230692475</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.696167292706434</v>
+        <v>-4.696696842118577</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-5.233135244689677</v>
+        <v>-5.185063752970294</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-9.175455835469869</v>
+        <v>-9.151834254783296</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-10.67869631124717</v>
+        <v>-10.63115569013176</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-13.26887825887083</v>
+        <v>-13.22009834446561</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-14.7501812685512</v>
+        <v>-14.67745558535301</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-16.31308261485594</v>
+        <v>-16.21427906664036</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-16.52530591198924</v>
+        <v>-16.42580798932101</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-19.33322617606168</v>
+        <v>-19.20985981203315</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-19.05326168761043</v>
+        <v>-18.9047607265318</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-19.54554942900912</v>
+        <v>-19.37355066944278</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>147</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.45843411480994</v>
+        <v>-1.48717743649258</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-12.51958088543009</v>
+        <v>-12.5211693423094</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-8.863553314959312</v>
+        <v>-8.863928817059794</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-9.415752657547898</v>
+        <v>-9.416451222543209</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-9.955053386006476</v>
+        <v>-9.907204916993116</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-10.33783120256169</v>
+        <v>-10.31432021643158</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-14.49487067540434</v>
+        <v>-14.44751683400289</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-12.25332094947094</v>
+        <v>-12.20462718578243</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-15.7119475919932</v>
+        <v>-15.63935092160693</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-13.17423497429461</v>
+        <v>-13.07550366243523</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-14.06510509010394</v>
+        <v>-13.96566838785251</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-15.39779814622418</v>
+        <v>-15.27447415846872</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-17.18577101040565</v>
+        <v>-17.03730133342873</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-17.64947184904112</v>
+        <v>-17.47747308947446</v>
       </c>
     </row>
     <row r="22">
@@ -1404,101 +1404,101 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.930486845985094</v>
+        <v>-7.593176007081716</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-4.42919283750043</v>
+        <v>-4.096934746828651</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.900165517783563</v>
+        <v>0.8422187068925879</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.075377427819902</v>
+        <v>1.945612358655843</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.483109960871218</v>
+        <v>-2.59346982209032</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.148536165566817</v>
+        <v>2.335418000081113</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.09167623690017734</v>
+        <v>-1.113430689095885</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>5.283613489981832</v>
+        <v>3.692648097505682</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>7.572361733808002</v>
+        <v>5.224823960164329</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>9.744967296929218</v>
+        <v>6.596272301438766</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>10.58510893504148</v>
+        <v>7.364178892951728</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>9.00598648689526</v>
+        <v>5.29717636817211</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>7.630779776852407</v>
+        <v>3.389684603186097</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>9.57501794687709</v>
+        <v>4.61658192383522</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 842.7</t>
+          <t>X ≈ 842.6</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>138</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.930191392853111</v>
+        <v>-3.959387187205742</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-9.889203572873626</v>
+        <v>-9.890390359318282</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-15.3564387257446</v>
+        <v>-15.35659211574892</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-19.57403966911285</v>
+        <v>-19.57453416149085</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-20.83696690336788</v>
+        <v>-20.78842098360211</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-21.98886823605155</v>
+        <v>-21.96491082710194</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-22.79821627647715</v>
+        <v>-22.75020459748682</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-23.26528492026396</v>
+        <v>-23.21603735787024</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-25.50018012026492</v>
+        <v>-25.42692301048522</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-27.07473659775428</v>
+        <v>-26.9753892724597</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-29.45335079949265</v>
+        <v>-29.35344276347397</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-32.31752337177493</v>
+        <v>-32.19382675074668</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-34.91158726856676</v>
+        <v>-34.76289772078893</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-36.1351269806589</v>
+        <v>-35.96312822109224</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>141</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.253965675924427</v>
+        <v>-4.283161470277058</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-4.446712052676197</v>
+        <v>-4.447898839120853</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-6.969143011899241</v>
+        <v>-6.969296401903563</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.711258293842789</v>
+        <v>-4.711752786220792</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-5.958767705094516</v>
+        <v>-5.910221785328744</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-5.661393675459507</v>
+        <v>-5.637436266509894</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.490784885789587</v>
+        <v>-1.442773206799266</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.376293245888384</v>
+        <v>-3.327045683494667</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.146495260567022</v>
+        <v>-4.073238150787326</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-6.414853773208939</v>
+        <v>-6.315506447914366</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.328774789625164</v>
+        <v>-7.228866753606489</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-10.13127606989412</v>
+        <v>-10.00757944886588</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-14.09752621398759</v>
+        <v>-13.94883666620976</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-13.16257070560511</v>
+        <v>-12.99057194603844</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>141</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.417086243300311</v>
+        <v>-1.446282037652942</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9006127618960562</v>
+        <v>-0.901799548340712</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.132263579275126</v>
+        <v>-4.132416969279447</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.711258293842789</v>
+        <v>-4.711752786220792</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9942286980023951</v>
+        <v>-0.9456827782366233</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.533734100991424</v>
+        <v>-3.509776692041811</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.909224602101474</v>
+        <v>-2.861212923111154</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.248633671420137</v>
+        <v>-1.19938610902642</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.1088238883689883</v>
+        <v>0.1820809981486846</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.6773448083512648</v>
+        <v>0.7766921336458381</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.891083366403045</v>
+        <v>1.99099140242172</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.343901235070504</v>
+        <v>3.467597856098749</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.888289388849302</v>
+        <v>8.036978936627129</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>9.532464755387885</v>
+        <v>9.704463514954547</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>138</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4176346941033273</v>
+        <v>0.388438899750696</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>6.052825412633702</v>
+        <v>6.051638626189046</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.310227940922054</v>
+        <v>1.310074550917733</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.063641490307525</v>
+        <v>5.063146997929522</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.525351937211909</v>
+        <v>4.57389785697768</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.272001329165846</v>
+        <v>6.295958738115459</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.085841694537343</v>
+        <v>9.133853373527664</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>11.566571337782</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>13.63025466234377</v>
+        <v>13.70351177212347</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>16.40352427181102</v>
+        <v>16.5028715971056</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>15.47418543239141</v>
+        <v>15.57409346841008</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>17.68247662822498</v>
+        <v>17.80617324925323</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>17.98696345607092</v>
+        <v>18.13565300384875</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>18.21269910629753</v>
+        <v>18.38469786586419</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>141</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.256672621947999</v>
+        <v>4.227476827595368</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>12.57456454306858</v>
+        <v>12.57337775662392</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>10.05213358384528</v>
+        <v>10.05198019384096</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>13.72845801821386</v>
+        <v>13.72796352583586</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>14.60860818143023</v>
+        <v>14.65715410119601</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>14.90598221106532</v>
+        <v>14.92993962001493</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>15.53049170995517</v>
+        <v>15.57850338894549</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>13.64498334985638</v>
+        <v>13.6942309122501</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>16.42088062595764</v>
+        <v>16.49413773573733</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>19.11706112040793</v>
+        <v>19.2164084457025</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>21.04001953661589</v>
+        <v>21.13992757263456</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>21.78361754712724</v>
+        <v>21.90731416815549</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>22.78190641012597</v>
+        <v>22.9305959579038</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>23.71686191850845</v>
+        <v>23.88886067807511</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>138</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4176346941032421</v>
+        <v>0.3884388997506107</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.704999325677093</v>
+        <v>1.703812539232437</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.310227940922225</v>
+        <v>1.310074550917903</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.7158154033510371</v>
+        <v>0.7153209109730341</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.076076574893072</v>
+        <v>3.124622494658844</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.822725966846996</v>
+        <v>4.846683375796609</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.564102564102569</v>
+        <v>2.61211424309289</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.0768791231623851</v>
+        <v>-0.02763156076866835</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.5867764014743386</v>
+        <v>0.660033511254035</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.360046010941495</v>
+        <v>3.459393336236069</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.2567941280435804</v>
+        <v>0.3567021640622556</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.158103081919933</v>
+        <v>-1.034406460891688</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.8536162540739198</v>
+        <v>-0.7049267062960922</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.546032439630871</v>
+        <v>1.718031199197533</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>141</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.417086243300346</v>
+        <v>-1.446282037652978</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.5178269544160017</v>
+        <v>0.5166401679713459</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.550703295587262</v>
+        <v>-5.550856685591583</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.711258293842832</v>
+        <v>-4.711752786220835</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-4.540327988782543</v>
+        <v>-4.491782069016772</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.533734100991424</v>
+        <v>-3.509776692041811</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-4.327664318413625</v>
+        <v>-4.279652639423304</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.248633671420258</v>
+        <v>-1.199386109026541</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4.85571511872314</v>
+        <v>-4.782458008943443</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-5.705633915052957</v>
+        <v>-5.606286589758383</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-5.910335073313227</v>
+        <v>-5.810427037294552</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-9.422056211738003</v>
+        <v>-9.298359590709758</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-9.132987206895386</v>
+        <v>-8.984297659117559</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-12.45335084744899</v>
+        <v>-12.28135208788233</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>138</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-8.278017479809677</v>
+        <v>-8.307213274162308</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-12.06311661635181</v>
+        <v>-12.06430340279646</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-10.28397495762858</v>
+        <v>-10.2841283476329</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-14.50157590099678</v>
+        <v>-14.50207039337479</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-15.03986545409244</v>
+        <v>-14.99131953432666</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-14.74249142445735</v>
+        <v>-14.71853401550774</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-19.17502787068004</v>
+        <v>-19.12701619168972</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-20.3667341956262</v>
+        <v>-20.31748663323248</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-20.42771635214901</v>
+        <v>-20.35445924236932</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-24.90082355427594</v>
+        <v>-24.80147622898136</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-26.55480007485492</v>
+        <v>-26.45489203883625</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-26.5204219224996</v>
+        <v>-26.39672530147136</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-22.59274668885649</v>
+        <v>-22.44405714107867</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-25.26556176326764</v>
+        <v>-25.09356300370098</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>141</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.001353473011747042</v>
+        <v>-0.02784232134088427</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.9006127618960562</v>
+        <v>-0.901799548340712</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5861642884950626</v>
+        <v>-0.586317678499384</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.292818577530731</v>
+        <v>-3.293313069908734</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.41266841431441</v>
+        <v>-2.364122494548639</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.406074526523341</v>
+        <v>-1.382117117573728</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.055314404990639</v>
+        <v>2.10332608398096</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.8790259030479035</v>
+        <v>0.9282734654416203</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.945703320993175</v>
+        <v>3.018960430772871</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.514224240975416</v>
+        <v>3.613571566269989</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.727962799027196</v>
+        <v>4.827870835045871</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.762340951382484</v>
+        <v>4.886037572410729</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.632970239913092</v>
+        <v>3.78165978769092</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.149486031983592</v>
+        <v>3.321484791550255</v>
       </c>
     </row>
     <row r="32">
@@ -1924,49 +1924,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.256672621947921</v>
+        <v>4.736264986707219</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>8.319245394132317</v>
+        <v>7.500913988507882</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>12.17979315831344</v>
+        <v>11.45500208714971</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.89157858558971</v>
+        <v>12.30952380952377</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.644069174337993</v>
+        <v>9.646361625093583</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12.77832263659722</v>
+        <v>12.81769786855024</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11.98439241917502</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12.22654363354429</v>
+        <v>12.29120901894138</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>15.00244090964566</v>
+        <v>15.15278713444231</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>17.69862140409589</v>
+        <v>17.9521469594244</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>17.4939202458358</v>
+        <v>17.74800651188838</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>21.07439768897125</v>
+        <v>20.70472397389096</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>22.07268655196987</v>
+        <v>21.75884140964593</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>25.1353016348205</v>
+        <v>24.90643699629899</v>
       </c>
     </row>
     <row r="33">
@@ -1976,101 +1976,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.919083969465653</v>
+        <v>1.396138175113016</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-3.692102123598183</v>
+        <v>-2.530788910042837</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.7131264916468041</v>
+        <v>1.762973101642459</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.7566483647648568</v>
+        <v>-2.013392857142861</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.105062082139462</v>
+        <v>1.403608001905233</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3.002436111774529</v>
+        <v>3.238893520724147</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.117725752508363</v>
+        <v>2.396987431498687</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4.050657108721623</v>
+        <v>4.274904671115344</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.789674952198851</v>
+        <v>5.019182061978547</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.539756155869007</v>
+        <v>1.851603481163565</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.135054997608783</v>
+        <v>2.42871303362746</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>2.169433149964121</v>
+        <v>3.268129770992367</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>1.749282296650712</v>
+        <v>2.872971844428541</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.97501794687723</v>
+        <v>3.122016706443894</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 1355</t>
+          <t>X ≈ 1354</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>94</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.417086243300311</v>
+        <v>-1.446282037652942</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.35470638704011</v>
+        <v>3.353519600595455</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.959935002285086</v>
+        <v>2.959781612280764</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.153989933107482</v>
+        <v>4.153495440729479</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2.551870592777725</v>
+        <v>2.600416512543497</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.913074409646875</v>
+        <v>3.937031818596488</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.019853412082831</v>
+        <v>7.067865091073152</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.616614555530134</v>
+        <v>7.665862117923851</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8.619462186241407</v>
+        <v>8.692719296021103</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.705713602677513</v>
+        <v>6.805060927972086</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.82016138058755</v>
+        <v>11.92006941660622</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>15.04602889464497</v>
+        <v>15.16972551567321</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>15.68970782856562</v>
+        <v>15.83839737634344</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.91544347879215</v>
+        <v>16.08744223835881</v>
       </c>
     </row>
   </sheetData>
@@ -2210,521 +2210,521 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 27.84</t>
+          <t>X &gt; 28</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4095</v>
+        <v>4103</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.02638679322416237</v>
+        <v>0.01661315081758374</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0867454155387648</v>
+        <v>-0.1200203802737008</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04308265336134554</v>
+        <v>0.03412040353842372</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08914944278690484</v>
+        <v>0.0800076412767794</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.07582231605757528</v>
+        <v>0.0660593637729292</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.00336452190813219</v>
+        <v>0.01165258177984896</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1202611011187997</v>
+        <v>0.1345938791872499</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.08108871076990454</v>
+        <v>0.09581608508467809</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2530895863451974</v>
+        <v>0.2670216432833215</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2217761607482345</v>
+        <v>0.2358407589819222</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2748304978528182</v>
+        <v>0.2889328339197306</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2741927301447404</v>
+        <v>0.2877704530873757</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2340479216507134</v>
+        <v>0.2474845149938432</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2050545769138736</v>
+        <v>0.2178916759784002</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 74.4</t>
+          <t>X &gt; 74.55</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3954</v>
+        <v>3965</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2793562154953975</v>
+        <v>0.2802350831069873</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1439039278390339</v>
+        <v>0.1435730462055886</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4185489380528296</v>
+        <v>0.4173996609985906</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.6635332699475498</v>
+        <v>0.66172506738544</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.618561955972396</v>
+        <v>0.6141012077431682</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.677549690775038</v>
+        <v>0.6743170042378637</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.7582710693475505</v>
+        <v>0.7534514294845849</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.7092429673074889</v>
+        <v>0.7044878995212898</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.8644413073390353</v>
+        <v>0.8578942786032329</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.7866485257527742</v>
+        <v>0.7788364113726871</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.7732152199994999</v>
+        <v>0.7654065820145775</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.8472895705910162</v>
+        <v>0.8379243260717715</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.7196994900767493</v>
+        <v>0.7092678605657099</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4794185538575206</v>
+        <v>0.4683281818537495</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 121</t>
+          <t>X &gt; 121.1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3816</v>
+        <v>3824</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1437901590712869</v>
+        <v>0.1351839791265661</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.06150289207579362</v>
+        <v>0.02558491686018982</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3080049865514027</v>
+        <v>0.2717736231548429</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.4264148866726813</v>
+        <v>0.3898576645055414</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1377418207015424</v>
+        <v>0.09751616783268702</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.3187541034063344</v>
+        <v>0.3063517670707085</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.326880866293358</v>
+        <v>0.2861237536077894</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.3189982913485281</v>
+        <v>0.2784947494443273</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.4819021178622975</v>
+        <v>0.464916914420435</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3010127003716079</v>
+        <v>0.2825726556672237</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.3729183126127182</v>
+        <v>0.3544299790155065</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4221308974759026</v>
+        <v>0.4012322278663873</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3574038580863999</v>
+        <v>0.3345731516180805</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.2049969825166542</v>
+        <v>0.1800710997493482</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 167.5</t>
+          <t>X &gt; 167.7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3675</v>
+        <v>3686</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2032587637230705</v>
+        <v>-0.198676301772629</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2814159288599143</v>
+        <v>-0.2804170874360281</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1189950493190395</v>
+        <v>-0.118620082019973</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.02829015580964267</v>
+        <v>-0.02813852813853401</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3618217397932355</v>
+        <v>-0.3673662876752957</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1310963346006986</v>
+        <v>-0.1339746438670772</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2010140628093993</v>
+        <v>-0.2069676862917262</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1914510140710988</v>
+        <v>-0.1976034545618006</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1288033086707117</v>
+        <v>-0.1384225844587306</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.3657616478820245</v>
+        <v>-0.3782406922781689</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2834333112547114</v>
+        <v>-0.2962378338162779</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2338303800875536</v>
+        <v>-0.2500372572072038</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3939168328378599</v>
+        <v>-0.4130669404914471</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.6426691279526935</v>
+        <v>-0.6642692403819197</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 214.1</t>
+          <t>X &gt; 214.2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3534</v>
+        <v>3545</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5215137187215575</v>
+        <v>-0.5146087332624774</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.6234050000787192</v>
+        <v>-0.6212619210071324</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6363798553207829</v>
+        <v>-0.63438347878499</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.6602601029138455</v>
+        <v>-0.6581273859754972</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.929372013259929</v>
+        <v>-0.9353058979259572</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.7861579029064387</v>
+        <v>-0.7880731271790395</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8556715928742946</v>
+        <v>-0.8617400459787845</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.9120547556851548</v>
+        <v>-0.9181747431341591</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.9294547454558497</v>
+        <v>-0.9398848394299009</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.25526928223163</v>
+        <v>-1.269434135066362</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.359658036035533</v>
+        <v>-1.373605173813338</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.422874542343564</v>
+        <v>-1.44095537138147</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.686078382274324</v>
+        <v>-1.707893919812861</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.925830949557387</v>
+        <v>-1.951149725149882</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 260.7</t>
+          <t>X &gt; 260.8</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3396</v>
+        <v>3407</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.8822067316197177</v>
+        <v>-0.8726849243021917</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.9524307620958297</v>
+        <v>-0.9490947012098445</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9206862468328154</v>
+        <v>-0.9176881037408009</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.009613720020283</v>
+        <v>-1.006250261298547</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.297287403910481</v>
+        <v>-1.304237431350053</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.07229949339586</v>
+        <v>-1.074338543697522</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.053123498152814</v>
+        <v>-1.060741771781927</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.122299975346571</v>
+        <v>-1.129981059913078</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.04978403045331</v>
+        <v>-1.063210962640447</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.354361491189827</v>
+        <v>-1.372799186675778</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.513547532547122</v>
+        <v>-1.531605881328531</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.61020192949438</v>
+        <v>-1.633417603604293</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.955398303879164</v>
+        <v>-1.983248812848458</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.331931405301795</v>
+        <v>-2.363931341692286</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 307.2</t>
+          <t>X &gt; 307.3</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3255</v>
+        <v>3266</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.042727536042307</v>
+        <v>-1.031002340288019</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.475022233791023</v>
+        <v>-1.46973796434424</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.455642644911705</v>
+        <v>-1.450713196801239</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.707337491870518</v>
+        <v>-1.701465201465204</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.861849682566437</v>
+        <v>-1.869292761453558</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.793395944615298</v>
+        <v>-1.794131830528151</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.800606558956993</v>
+        <v>-1.808109192393772</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.914138966102051</v>
+        <v>-1.921611221305199</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.682717685837957</v>
+        <v>-1.697752743891222</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.994579529924202</v>
+        <v>-2.015942390396063</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.12129859355143</v>
+        <v>-2.142400074356615</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.162405965786569</v>
+        <v>-2.190101563156958</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.412388465020044</v>
+        <v>-2.446319554408312</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.753707091525214</v>
+        <v>-2.793093520132942</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 353.8</t>
+          <t>X &gt; 353.9</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3117</v>
+        <v>3128</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.043216350023165</v>
+        <v>-1.02969157655842</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.51939518847513</v>
+        <v>-1.513671075647927</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.641604966153736</v>
+        <v>-1.635800393101086</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.81427548340892</v>
+        <v>-1.807748338341078</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.983869459767142</v>
+        <v>-1.993347688244612</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.861563888225461</v>
+        <v>-1.863147295602374</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.769342109207379</v>
+        <v>-1.779398134689515</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.899262840045587</v>
+        <v>-1.909284863026329</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.751004099690959</v>
+        <v>-1.769688429563104</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.071137788379652</v>
+        <v>-2.097550414111019</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.226483463929668</v>
+        <v>-2.252548943376674</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.206841296974005</v>
+        <v>-2.241055532522005</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.481378383272315</v>
+        <v>-2.52312115653023</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.623249618089062</v>
+        <v>-2.67242063370955</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 400.3</t>
+          <t>X &gt; 400.4</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2976</v>
+        <v>2987</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.192859824445357</v>
+        <v>-1.176778491553655</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.682463569381319</v>
+        <v>-1.675816419212559</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.825340197338825</v>
+        <v>-1.818581267937262</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.012375089480201</v>
+        <v>-2.004790504790513</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.499628035113489</v>
+        <v>-2.509943399963944</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.184695255517688</v>
+        <v>-2.186294292297553</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.318881689663939</v>
+        <v>-2.32965335006444</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.198303320520488</v>
+        <v>-2.210018482910712</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.040247892484139</v>
+        <v>-2.062201627861022</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.301854582386042</v>
+        <v>-2.333347204225937</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.555646580101836</v>
+        <v>-2.586441648646776</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.603971819814255</v>
+        <v>-2.64417367497618</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.838154720480624</v>
+        <v>-2.887570324246155</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.997562698284042</v>
+        <v>-3.05579547969603</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 446.9</t>
+          <t>X &gt; 447</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2838</v>
+        <v>2849</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.200663487566977</v>
+        <v>-1.182368987710177</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.635961772720989</v>
+        <v>-1.629115544086879</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.73152075300046</v>
+        <v>-1.724789136119782</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.109457353528896</v>
+        <v>-2.101109278968671</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.488896470723212</v>
+        <v>-2.502095287108077</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.243382581127783</v>
+        <v>-2.245990098456808</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.485437692131349</v>
+        <v>-2.498408226764617</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.477050345568109</v>
+        <v>-2.490638236065045</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.589853714702308</v>
+        <v>-2.614292885463641</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.893459889169712</v>
+        <v>-2.929000269274574</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.114645811965289</v>
+        <v>-3.14960919638655</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.237609103557006</v>
+        <v>-3.283299552052178</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.462975540615936</v>
+        <v>-3.519572015220582</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.641331595053693</v>
+        <v>-3.708230748803544</v>
       </c>
     </row>
     <row r="16">
@@ -2734,101 +2734,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2697</v>
+        <v>2708</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.300104222416273</v>
+        <v>-1.27894681202406</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.711149742645794</v>
+        <v>-1.703583027689895</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.012722843656029</v>
+        <v>-2.004496556320028</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.380290773335233</v>
+        <v>-2.370387890255444</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.677643017638822</v>
+        <v>-2.693281950247894</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.545807880831752</v>
+        <v>-2.548569660424597</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.83316182145613</v>
+        <v>-2.847890561134825</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.837097238300203</v>
+        <v>-2.852490317830856</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.915728452686423</v>
+        <v>-2.943923817122084</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.005819556830012</v>
+        <v>-3.04791716780398</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.190870928317125</v>
+        <v>-3.232539732879346</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.470285264263374</v>
+        <v>-3.523844398749333</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.722622818249214</v>
+        <v>-3.788849860997807</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.92220118549205</v>
+        <v>-4.000398360025812</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 540</t>
+          <t>X &gt; 540.1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2556</v>
+        <v>2567</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.64401451243392</v>
+        <v>-1.618638956669926</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.145061625155819</v>
+        <v>-2.135165606436786</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.558552511080137</v>
+        <v>-2.547538923182984</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.070600040524795</v>
+        <v>-3.057181661954658</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.432949613766986</v>
+        <v>-3.448876470144469</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-3.27151084610378</v>
+        <v>-3.272635605489441</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.609312874101079</v>
+        <v>-3.62416155840031</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.549030635228412</v>
+        <v>-3.564922379020686</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.628911537453632</v>
+        <v>-3.659618482344939</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.755556344131008</v>
+        <v>-3.802203403317186</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.9007402349039</v>
+        <v>-3.947138133687695</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-4.236821736666059</v>
+        <v>-4.296827410790428</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-4.558422044373927</v>
+        <v>-4.632869277066789</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-4.742665934186924</v>
+        <v>-4.831090032940587</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2418</v>
+        <v>2429</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.431964981583299</v>
+        <v>-1.404460719235878</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.540661794380078</v>
+        <v>-1.5328628551473</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.996136579575946</v>
+        <v>-1.987026898357541</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.338526453726963</v>
+        <v>-2.327622561939911</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.566960991614152</v>
+        <v>-2.590444500145644</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.289237424911377</v>
+        <v>-2.296216245381729</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.558562907285456</v>
+        <v>-2.581717412507878</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.344062363225575</v>
+        <v>-2.369089168720386</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.176895415114394</v>
+        <v>-2.220058899401899</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.385594793759417</v>
+        <v>-2.446716494175519</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.402904523250349</v>
+        <v>-2.464379071635676</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.048748668217691</v>
+        <v>-3.124558423166413</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.198878100207494</v>
+        <v>-3.292151612361579</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.32324508041804</v>
+        <v>-3.432892721304135</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2277</v>
+        <v>2288</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.432881096036532</v>
+        <v>-1.401898004808757</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.317964945791282</v>
+        <v>-1.310680214390658</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.864495885975593</v>
+        <v>-1.855447950989124</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.929888417235347</v>
+        <v>-1.920241203531027</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.095287874116025</v>
+        <v>-2.125451641107404</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.643515748181699</v>
+        <v>-1.6554880123769</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.011521182693031</v>
+        <v>-2.041669975908725</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.623280692417225</v>
+        <v>-1.656328981892507</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.354058614847602</v>
+        <v>-1.408328295631577</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.478919863420792</v>
+        <v>-1.554264756183734</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.571962546250852</v>
+        <v>-1.647359096446728</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.99625355473092</v>
+        <v>-2.089402980099329</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.041411294218463</v>
+        <v>-2.155151790346466</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.099114683777131</v>
+        <v>-2.232004272577072</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2139</v>
+        <v>2150</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.040395584437704</v>
+        <v>-1.007569060208304</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.9075368051416461</v>
+        <v>-0.901799548340712</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.51012932230671</v>
+        <v>-1.502297606363094</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.680985265648992</v>
+        <v>-1.671957671957671</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.589537545421074</v>
+        <v>-1.627309089340727</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.174182425719643</v>
+        <v>-1.190844662779092</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.560186642645412</v>
+        <v>-1.597637626452176</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.116708858644344</v>
+        <v>-1.157609243541422</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.9192802716817496</v>
+        <v>-0.9839356874414023</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.9039209323251285</v>
+        <v>-0.9933941975736715</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.98950149165357</v>
+        <v>-1.079110352345587</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.443084365215697</v>
+        <v>-1.552966883282728</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.463801815498826</v>
+        <v>-1.597332665101909</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.352518285006809</v>
+        <v>-1.50879724704447</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1998</v>
+        <v>2009</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.163163668525399</v>
+        <v>-1.125344268012604</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.8085200340459409</v>
+        <v>-0.8028386379003294</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.276320994664815</v>
+        <v>-1.269205116179322</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.468202149625419</v>
+        <v>-1.459668860114625</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.332406776854079</v>
+        <v>-1.377611026836114</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6095279959024396</v>
+        <v>-0.6321092060978657</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9166882125789186</v>
+        <v>-0.9636276478663959</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2591233304001364</v>
+        <v>-0.3110134430285711</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.0567743031723893</v>
+        <v>-0.0228673421922565</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.1835123996252435</v>
+        <v>0.07487099234091232</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.10686909056232</v>
+        <v>-0.002015097585250203</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1805668500358806</v>
+        <v>-0.3137324865909221</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.222503596295752</v>
+        <v>-0.38262517049683</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.06862569676640362</v>
+        <v>-0.2549743338746566</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1851</v>
+        <v>1862</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.139714313796155</v>
+        <v>-1.09677849155365</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1215318001806693</v>
+        <v>0.1222927335003803</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.67376931930918</v>
+        <v>-0.669621666109812</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.8370352535343315</v>
+        <v>-0.8315018315018392</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6476260899035609</v>
+        <v>-0.7042220355079323</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1630601031677514</v>
+        <v>0.1322758736653284</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1616439441122424</v>
+        <v>0.1008899194601653</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.6934142438858757</v>
+        <v>0.6279560629782992</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.309071503922986</v>
+        <v>1.210012940393113</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.244338366111577</v>
+        <v>1.11305846508639</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.232358125979893</v>
+        <v>1.100378583225329</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.027932880131424</v>
+        <v>0.867378698030997</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.12466026641313</v>
+        <v>0.9322176844714818</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.327584127320243</v>
+        <v>1.104696620514801</v>
       </c>
     </row>
     <row r="23">
@@ -3101,98 +3101,98 @@
         <v>1701</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.4526973356489847</v>
+        <v>-0.481893130001616</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.522830269111985</v>
+        <v>0.5216434826673293</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.8125642784884377</v>
+        <v>-0.8127176684927591</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.093861768644935</v>
+        <v>-1.094356261022938</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5739502635395652</v>
+        <v>-0.5254043437737934</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1002093908709654</v>
+        <v>-0.0762519819213523</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1678139359298854</v>
+        <v>0.215825614920206</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2886347689215043</v>
+        <v>0.3378823313152211</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.7567531414992601</v>
+        <v>0.8300102512789564</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.4947238219477725</v>
+        <v>0.5940711472423459</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.407600559043253</v>
+        <v>0.5075085950619282</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3244008160429033</v>
+        <v>0.4480974370711479</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.5509283871856852</v>
+        <v>0.6996179349635128</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.6002971943787188</v>
+        <v>0.7722959539453811</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 866</t>
+          <t>X &gt; 865.9</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1563</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.1456633114044763</v>
+        <v>-0.1748591057571076</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.442126923106869</v>
+        <v>1.440940136662213</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4715397993883101</v>
+        <v>0.4713864093839888</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.5377854164251659</v>
+        <v>0.5372909240471628</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.215106867808039</v>
+        <v>1.263652787573811</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.832378530200636</v>
+        <v>1.856335939150249</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.195524856794997</v>
+        <v>2.243536535785317</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.368251478523291</v>
+        <v>2.417499040917008</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.075023640618554</v>
+        <v>3.14828075039825</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.928879636355241</v>
+        <v>3.028226961649814</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.044076110852565</v>
+        <v>3.14398414687124</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.206413316310886</v>
+        <v>3.330109937339131</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.681975834718529</v>
+        <v>3.830665382496356</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.843731958393555</v>
+        <v>4.015730717960217</v>
       </c>
     </row>
     <row r="25">
@@ -3205,98 +3205,98 @@
         <v>1422</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.2617000032209233</v>
+        <v>0.232504208868292</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.026041336317434</v>
+        <v>2.024854549872778</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.209329023292348</v>
+        <v>1.209175633288027</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.058260214700681</v>
+        <v>1.057765722322678</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.926440422505131</v>
+        <v>1.974986342270903</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.575431892365252</v>
+        <v>2.599389301314865</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.561045021144096</v>
+        <v>2.609056700134417</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.937858233897444</v>
+        <v>2.987105796291161</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.791081421959746</v>
+        <v>3.864338531739442</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.855367970214985</v>
+        <v>3.954715295509558</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.072607740224825</v>
+        <v>4.1725157762435</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.528926820850202</v>
+        <v>4.652623441878447</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.444922240391925</v>
+        <v>5.593611788169753</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.53001091452844</v>
+        <v>5.702009674095102</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 959.1</t>
+          <t>X &gt; 959</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1281</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4464844378497261</v>
+        <v>0.4172886434970948</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.348178906846783</v>
+        <v>2.346992120402128</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.797279497111255</v>
+        <v>1.797126107106934</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.69331260322889</v>
+        <v>1.692818110850887</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.247869367043855</v>
+        <v>3.271826775993468</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.163159007777686</v>
+        <v>3.211170686768007</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.398666476403122</v>
+        <v>3.447914038796839</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.196388457273009</v>
+        <v>4.269645567052706</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.205173798335814</v>
+        <v>4.304521123630387</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.312728690036593</v>
+        <v>4.412636726055268</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.659362892352881</v>
+        <v>4.783059513381126</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.175980188922381</v>
+        <v>5.324669736700208</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.089459789187941</v>
+        <v>5.261458548754604</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1143</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4499676090107059</v>
+        <v>0.4207718146580746</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.900898751292459</v>
+        <v>1.899711964847803</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.856083622005485</v>
+        <v>1.855930232001164</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.286396254657717</v>
+        <v>1.285901762279714</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.972953595700254</v>
+        <v>2.021499515466026</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.882751072404453</v>
+        <v>2.906708481354066</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.44808445767022</v>
+        <v>2.49609613666054</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.418461133218564</v>
+        <v>2.467708695612281</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.057391487631918</v>
+        <v>3.130648597411614</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.73240707450416</v>
+        <v>2.831754399798733</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.96515123557905</v>
+        <v>3.065059271597725</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.087018451801391</v>
+        <v>3.210715072829636</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.629247301025174</v>
+        <v>3.777936848803002</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.505026695783627</v>
+        <v>3.677025455350289</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>1002</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.08570644969603336</v>
+        <v>-0.1149022440486647</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.3989158404736699</v>
+        <v>0.3977290540290142</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.7027472501298178</v>
+        <v>0.7025938601254964</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.4644327959025816</v>
+        <v>-0.4649272882805846</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1948824414208872</v>
+        <v>0.243428361186659</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.190859265467147</v>
+        <v>1.21481667441676</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.6071469101929949</v>
+        <v>0.6551585891833156</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8386810608174358</v>
+        <v>0.8879286232111525</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.176900501101052</v>
+        <v>1.250157610880748</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4267821039727906</v>
+        <v>0.5261294292673639</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4216817441157872</v>
+        <v>0.5215897801344624</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4560598964711104</v>
+        <v>0.5797565174993551</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.9341126359720704</v>
+        <v>1.082802183749898</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.6608462901906194</v>
+        <v>0.8328450497572817</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>864</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1661012157195358</v>
+        <v>-0.1952970100721672</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.1903052838092236</v>
+        <v>0.1891184973645679</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.6057190842393751</v>
+        <v>0.6055656942350538</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6529446610611487</v>
+        <v>-0.6534391534391517</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2653082882309263</v>
+        <v>-0.2167623684651545</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.61076944510787</v>
+        <v>0.6347268540574831</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.2945776043602137</v>
+        <v>0.3425892833505344</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.9849163679808797</v>
+        <v>1.034163930374596</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.271156433680325</v>
+        <v>1.344413543460021</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.04172532561248232</v>
+        <v>0.05762199968209103</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.4480179605717609</v>
+        <v>0.5479259965904362</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.7138775944085651</v>
+        <v>0.8375742154368098</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.219652667021087</v>
+        <v>1.368342214798915</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.5194623913216887</v>
+        <v>0.691461150888351</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>723</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.07786681870493339</v>
+        <v>0.04867102435230208</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1264317629854972</v>
+        <v>0.1252449765408414</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.806349174910956</v>
+        <v>1.806195784906635</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.1385106947095522</v>
+        <v>0.1380162023315492</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.5684092467314272</v>
+        <v>0.6169551664971991</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.419033622147978</v>
+        <v>1.442991031097591</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.196010676436444</v>
+        <v>1.244022355426765</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.420504964876535</v>
+        <v>1.469752527270252</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.466023499916687</v>
+        <v>2.539280609696384</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1.062854357805364</v>
+        <v>1.162201683099937</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.688028718217382</v>
+        <v>1.787936754236057</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.690594975690267</v>
+        <v>2.814291596718512</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.238632227494421</v>
+        <v>3.387321775272248</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.049430118384855</v>
+        <v>3.221428877951517</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>585</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.048998499380176</v>
+        <v>2.019802705027544</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.001914970418909</v>
+        <v>3.000728183974253</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.658425636945928</v>
+        <v>4.658272246941607</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.592069583953098</v>
+        <v>3.591575091575095</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.250361227438596</v>
+        <v>4.298907147204368</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.231495940834364</v>
+        <v>5.255453349783977</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.001486436269047</v>
+        <v>6.049498115259368</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.560058818123338</v>
+        <v>6.609306380517054</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.866598029121924</v>
+        <v>7.939855138901621</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.187619403732235</v>
+        <v>7.286966729026808</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.350439612993412</v>
+        <v>8.450347649012087</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>9.581398961929928</v>
+        <v>9.705095582958172</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.332188279556689</v>
+        <v>9.480877827334517</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.728864100723392</v>
+        <v>9.900862860290054</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>444</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.699264149645828</v>
+        <v>2.670068355293196</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>4.240044423290499</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.323937302457594</v>
+        <v>6.323783912453273</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.778486770370272</v>
+        <v>5.777992277992269</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.366323343400701</v>
+        <v>6.414869263166473</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.339373048711472</v>
+        <v>7.363330457661085</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.254662689445304</v>
+        <v>7.302674368435625</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.364170622235136</v>
+        <v>8.413418184628853</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.429314591838491</v>
+        <v>9.502571701618187</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.354170570283401</v>
+        <v>8.453517895577974</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.500820763374577</v>
+        <v>9.600728799393252</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>11.11177549230647</v>
+        <v>11.23547211333472</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.14207508944351</v>
+        <v>11.29076463722134</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>11.81826119012049</v>
+        <v>11.99025994968715</v>
       </c>
     </row>
     <row r="33">
@@ -3618,101 +3618,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.974529514020105</v>
+        <v>1.738254188184911</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.343541440758251</v>
+        <v>2.769456187996376</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.598935072504872</v>
+        <v>4.009705127786255</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.399127212792898</v>
+        <v>2.832399626517265</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.841035679499186</v>
+        <v>4.957529570532671</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.808376705833936</v>
+        <v>4.903517703730685</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.053699349868104</v>
+        <v>5.169659000126138</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.566828725883347</v>
+        <v>6.664610553468286</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.835879572660893</v>
+        <v>6.954435329952403</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.005762756529066</v>
+        <v>4.16982243541193</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.781259618070841</v>
+        <v>5.92646630160133</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.47570377702683</v>
+        <v>6.965025195828964</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.055552923713421</v>
+        <v>6.569867269265139</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.621222567339288</v>
+        <v>6.165317360038678</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 1332</t>
+          <t>X &gt; 1331</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>178</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.013465991937558</v>
+        <v>1.984270197584927</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>6.58205517977261</v>
+        <v>6.580868393327954</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.625486042208578</v>
+        <v>5.625332652204257</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6.317508938605933</v>
+        <v>6.31701444622793</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.464612643937194</v>
+        <v>7.513158563702966</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>6.076593415145325</v>
+        <v>6.100550824094938</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.115478561497127</v>
+        <v>7.163490240487448</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.333803176137359</v>
+        <v>8.383050738531075</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8.272821019614582</v>
+        <v>8.346078129394279</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.737508964857753</v>
+        <v>5.836856290152326</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.341796570642515</v>
+        <v>8.44170460666119</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>9.499770228615809</v>
+        <v>9.623466849644053</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>9.0796193753024</v>
+        <v>9.228308923080228</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.181759519910962</v>
+        <v>8.353758279477624</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>5.852417302798983</v>
+        <v>5.823221508446352</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>10.19361216211611</v>
+        <v>10.19242537567145</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8.608364586884875</v>
+        <v>8.608211196880553</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>8.738589730473237</v>
+        <v>8.738095238095234</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>12.96220493928231</v>
+        <v>13.01075085904808</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>8.497674207012629</v>
+        <v>8.521631615962242</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>7.222487657270271</v>
+        <v>7.270499336260592</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>9.136371394435919</v>
+        <v>9.185618956829636</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.884913047436946</v>
+        <v>7.958170157216642</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>4.6540418701547</v>
+        <v>4.753389195449273</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4.449340711894507</v>
+        <v>4.549248747913182</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3.293242673773648</v>
+        <v>3.416939294801892</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1.682615629984049</v>
+        <v>1.831305177761877</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.4726011007417981</v>
+        <v>-0.3006023411751357</v>
       </c>
     </row>
   </sheetData>
@@ -3904,521 +3904,521 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 27.84</t>
+          <t>X &lt; 28</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.290439840058163</v>
+        <v>-1.319635634410794</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>4.240044423290499</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.105921127400833</v>
+        <v>-2.106074517405155</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.704461727384363</v>
+        <v>-3.655915807618591</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1643408736793006</v>
+        <v>0.1882982826289137</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-5.872750437967824</v>
+        <v>-5.824738758977503</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.958866700802183</v>
+        <v>-3.909619138408466</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-12.35318219065829</v>
+        <v>-12.2799250808786</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-10.82214860603577</v>
+        <v>-10.72280128074119</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-13.40780214524835</v>
+        <v>-13.30789410922967</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-13.37342399289302</v>
+        <v>-13.24972737186478</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-11.41262246525405</v>
+        <v>-11.26393291747622</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.996410624551324</v>
+        <v>-9.824411864984661</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 74.4</t>
+          <t>X &lt; 74.55</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>225</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.925360474978795</v>
+        <v>-4.954556269331427</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.536546568042624</v>
+        <v>-2.53773335448728</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-7.375762397242113</v>
+        <v>-7.375915787246434</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-11.68998169809819</v>
+        <v>-11.69047619047619</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10.89493791786055</v>
+        <v>-10.84639199809478</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-11.93089722155879</v>
+        <v>-11.90693981260918</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-13.3489409141583</v>
+        <v>-13.30092923516798</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-12.4826762246117</v>
+        <v>-12.43342866221798</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-15.21032504780115</v>
+        <v>-15.13706793802145</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-13.83802162190879</v>
+        <v>-13.73867429661421</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-13.59827833572453</v>
+        <v>-13.49837029970585</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-14.89723351670254</v>
+        <v>-14.7735368956743</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-12.65071770334929</v>
+        <v>-12.50202815557146</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-8.424982053122754</v>
+        <v>-8.252983293556092</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 121</t>
+          <t>X &lt; 121.1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.516728702710658</v>
+        <v>-1.417215650023593</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.648575952799284</v>
+        <v>-0.2681522980209721</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.247204086865622</v>
+        <v>-2.847682636062459</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.494389411596813</v>
+        <v>-4.083918813427012</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.451411747061655</v>
+        <v>-1.021255386072916</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.357894466737868</v>
+        <v>-3.207486260696619</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.442604826004036</v>
+        <v>-2.99491830620623</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.358709282462947</v>
+        <v>-2.914302979157874</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.072584000969201</v>
+        <v>-4.863843894305603</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.167681860659933</v>
+        <v>-2.955432037962112</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.923347206247954</v>
+        <v>-3.706020572929901</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.439933241220452</v>
+        <v>-4.194301922996701</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-3.758155719878211</v>
+        <v>-3.496563674697136</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.155009601332118</v>
+        <v>-1.881398594102535</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 167.5</t>
+          <t>X &lt; 167.7</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>504</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.487337937719616</v>
+        <v>1.458142143366985</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.058691527195471</v>
+        <v>2.057504740750815</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.8702693487896411</v>
+        <v>0.8701159587853198</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.206843698727198</v>
+        <v>0.206349206349195</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.644744621821985</v>
+        <v>2.693290541587757</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>0.9819490762797045</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.468519403302018</v>
+        <v>1.516531082292339</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.398276156340671</v>
+        <v>1.447523718734388</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.9404686029925031</v>
+        <v>1.013725712772199</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.669914886027726</v>
+        <v>2.7692622113223</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.068388330942135</v>
+        <v>2.16829636696081</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.705941086472066</v>
+        <v>1.829637707500311</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.873091820460239</v>
+        <v>3.021781368238067</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.68612905798836</v>
+        <v>4.858127817555022</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 214.1</t>
+          <t>X &lt; 214.2</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>645</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.867921178767972</v>
+        <v>2.838725384415341</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.427277721363055</v>
+        <v>3.426090934918399</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.497622615677784</v>
+        <v>3.497469225673463</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.627847759266146</v>
+        <v>3.627353266888143</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.105062082139447</v>
+        <v>5.153608001905219</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.317164793945082</v>
+        <v>4.341122202894695</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.697570713748682</v>
+        <v>4.745582392739003</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.005695868411557</v>
+        <v>5.054943430805274</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.099752471578697</v>
+        <v>5.173009581358393</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.885492589977517</v>
+        <v>6.98483991527209</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.455985230166938</v>
+        <v>7.555893266185613</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7.800440901902114</v>
+        <v>7.924137522930359</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>9.240755164867764</v>
+        <v>9.389444712645592</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>10.55176213292376</v>
+        <v>10.72376089249043</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 260.7</t>
+          <t>X &lt; 260.8</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>783</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.840923049925415</v>
+        <v>3.811727255572784</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.145445769122126</v>
+        <v>4.144258982677471</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.006102226001829</v>
+        <v>4.005948835997508</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.391755211224925</v>
+        <v>4.391260718846922</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.6414605495724</v>
+        <v>5.690006469338172</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.661695371033787</v>
+        <v>4.6856527799834</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.576985011767619</v>
+        <v>4.624996690757939</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.876199892885104</v>
+        <v>4.925447455278821</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.559789894727594</v>
+        <v>4.63304700450729</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.881007752293002</v>
+        <v>5.980355077587575</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.57030403975439</v>
+        <v>6.670212075773065</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.987823954561826</v>
+        <v>7.11152057559007</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8.48338191350895</v>
+        <v>8.632071461286777</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>10.11397069272655</v>
+        <v>10.28596945229321</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 307.2</t>
+          <t>X &lt; 307.3</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>924</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.687915138296816</v>
+        <v>3.658719343944185</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.215257183761125</v>
+        <v>5.214070397316469</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.145161123681419</v>
+        <v>5.145007733677097</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.032962024845538</v>
+        <v>6.032467532467535</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.576923554000913</v>
+        <v>6.625469473766685</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6.333172042510469</v>
+        <v>6.357129451460082</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.3566867914694</v>
+        <v>6.404698470459721</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6.755419013483532</v>
+        <v>6.804666575877249</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.936861099384998</v>
+        <v>6.010118209164695</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>7.034994251107086</v>
+        <v>7.13434157640166</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>7.479643742197545</v>
+        <v>7.579551778216221</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>7.622247002777975</v>
+        <v>7.74594362380622</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>8.500797448165869</v>
+        <v>8.649486995943697</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>9.700559072418365</v>
+        <v>9.872557831985027</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 353.8</t>
+          <t>X &lt; 353.9</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1062</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.074639525021205</v>
+        <v>3.045443730668573</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.476636106156995</v>
+        <v>4.47544931971234</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.835160389951859</v>
+        <v>4.835006999947538</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.342033367815183</v>
+        <v>5.34153887543718</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.839525358975607</v>
+        <v>5.888071278741378</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.477765678629531</v>
+        <v>5.501723087579144</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.204731402225882</v>
+        <v>5.252743081216202</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.585120385557786</v>
+        <v>5.634367947951503</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.147490394760055</v>
+        <v>5.220747504539752</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.08664881123623</v>
+        <v>6.185996136530804</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.5410813629572</v>
+        <v>6.640989398975876</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.481297556743783</v>
+        <v>6.604994177772028</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>7.285252164823973</v>
+        <v>7.433941712601801</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>7.699311732187986</v>
+        <v>7.871310491754649</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 400.3</t>
+          <t>X &lt; 400.4</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1203</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.963805498975205</v>
+        <v>2.934609704622574</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.178887070084286</v>
+        <v>4.177700283639631</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.532245361139715</v>
+        <v>4.532091971135394</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.994972582866062</v>
+        <v>4.994478090488059</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.202318939994811</v>
+        <v>6.250864859760583</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.419061215681431</v>
+        <v>5.443018624631044</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.749978454087746</v>
+        <v>5.797990133078066</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.44916084937001</v>
+        <v>5.498408411763727</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.055676614709242</v>
+        <v>5.128933724488938</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.702017170000332</v>
+        <v>5.801364495294905</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>6.328571207085105</v>
+        <v>6.42847924310378</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>6.446074878974926</v>
+        <v>6.569771500003171</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>7.023430260075493</v>
+        <v>7.172119807853321</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.415416949371007</v>
+        <v>7.587415708937669</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 446.9</t>
+          <t>X &lt; 447</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1341</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.552641016445513</v>
+        <v>2.523445222092882</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.476876250749321</v>
+        <v>3.475689464304665</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.678674590080789</v>
+        <v>3.678521200076467</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.480040673266465</v>
+        <v>4.479546180888462</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5.284032999365394</v>
+        <v>5.332578919131166</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.76112365838155</v>
+        <v>4.785081067331163</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.272983023201874</v>
+        <v>5.320994702192195</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>5.253341672480019</v>
+        <v>5.302589234873736</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.490644378000496</v>
+        <v>5.563901487780193</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>6.132149891886883</v>
+        <v>6.231497217181456</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>6.598589673224019</v>
+        <v>6.698497709242694</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.856681472111774</v>
+        <v>6.980378093140018</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.331385204928118</v>
+        <v>7.480074752705946</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7.706263286176274</v>
+        <v>7.878262045742936</v>
       </c>
     </row>
     <row r="16">
@@ -4431,98 +4431,98 @@
         <v>1482</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.377383564607349</v>
+        <v>2.348187770254718</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.127870885848509</v>
+        <v>3.126684099403853</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.677768866815477</v>
+        <v>3.677615476811155</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.34780507653069</v>
+        <v>4.347310584152687</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.889137655688707</v>
+        <v>4.937683575454479</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.646700619196942</v>
+        <v>4.670658028146555</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.169277709323488</v>
+        <v>5.217289388313809</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>5.174543748397745</v>
+        <v>5.223791310791462</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.315990741672536</v>
+        <v>5.389247851452232</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.478217694330532</v>
+        <v>5.577565019625105</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>5.813327602197191</v>
+        <v>5.913235638215866</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.32004043741351</v>
+        <v>6.443737058441755</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.777082566556246</v>
+        <v>6.925772114334073</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>7.137770983314496</v>
+        <v>7.309769742881159</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 540</t>
+          <t>X &lt; 540.1</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1623</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.602263267062689</v>
+        <v>2.573067472710058</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.394034660135638</v>
+        <v>3.392847873690982</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.046706282158183</v>
+        <v>4.046552892153862</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4.854688665426146</v>
+        <v>4.854194173048143</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.425456413624353</v>
+        <v>5.474002333390125</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5.168301792612496</v>
+        <v>5.192259201562109</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>5.699734378509589</v>
+        <v>5.74774605749991</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5.602351501820827</v>
+        <v>5.651599064214544</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.726212228847032</v>
+        <v>5.799469338626729</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>5.923736439294743</v>
+        <v>6.023083764589316</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.150335342648845</v>
+        <v>6.25024337866752</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>6.677627851134794</v>
+        <v>6.801324472163039</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.181691415566306</v>
+        <v>7.330380963344133</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>7.469041360309156</v>
+        <v>7.641040119875818</v>
       </c>
     </row>
     <row r="18">
@@ -4535,46 +4535,46 @@
         <v>1761</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.976778461231689</v>
+        <v>1.947582666879057</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.125955798037253</v>
+        <v>2.124769011592598</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.753330920948315</v>
+        <v>2.753177530943994</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.224271567092039</v>
+        <v>3.223777074714036</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.537770770384761</v>
+        <v>3.586316690150532</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.153713794909116</v>
+        <v>3.177671203858729</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.52329077238344</v>
+        <v>3.571302451373761</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.226579879874386</v>
+        <v>3.275827442268103</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.995239972073925</v>
+        <v>3.068497081853621</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.281039517595282</v>
+        <v>3.380386842889855</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.303482027705336</v>
+        <v>3.403390063724011</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>4.189648936449075</v>
+        <v>4.313345557477319</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.394143171153843</v>
+        <v>4.54283271893167</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4.563092904287814</v>
+        <v>4.735091663854476</v>
       </c>
     </row>
     <row r="19">
@@ -4587,46 +4587,46 @@
         <v>1902</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.725182812788461</v>
+        <v>1.695987018435829</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.586131314887623</v>
+        <v>1.584944528442968</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.24288464096329</v>
+        <v>2.242731250958968</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.320533549010115</v>
+        <v>2.320039056632112</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.518311293495913</v>
+        <v>2.566857213261684</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.974465554466441</v>
+        <v>1.998422963416054</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.415517550615618</v>
+        <v>2.463529229605939</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.94844890682888</v>
+        <v>1.997696469222596</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.624585572598434</v>
+        <v>1.697842682378131</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.773615251557736</v>
+        <v>1.872962576852309</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.884371506546763</v>
+        <v>1.984279542565439</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.391935778775903</v>
+        <v>2.515632399804147</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.44497104533631</v>
+        <v>2.593660593114137</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.512977988938232</v>
+        <v>2.684976748504894</v>
       </c>
     </row>
     <row r="20">
@@ -4639,46 +4639,46 @@
         <v>2040</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.097515342014667</v>
+        <v>1.068319547662036</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9569174842449613</v>
+        <v>0.9557306978003055</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.591557864195799</v>
+        <v>1.591404474191478</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.770802615627296</v>
+        <v>1.770308123249293</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.673689533119841</v>
+        <v>1.722235452885613</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.23576944510787</v>
+        <v>1.259726854057483</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.641255164273069</v>
+        <v>1.68926684326339</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.17418652048633</v>
+        <v>1.223434082880047</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.9661455404341481</v>
+        <v>1.039402650213844</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.9495600774376172</v>
+        <v>1.048907402732191</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.038976566236244</v>
+        <v>1.138884602254919</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.514531189179806</v>
+        <v>1.638227810208051</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.535556806454636</v>
+        <v>1.684246354232464</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.418155201779214</v>
+        <v>1.590153961345877</v>
       </c>
     </row>
     <row r="21">
@@ -4691,46 +4691,46 @@
         <v>2181</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.07249983374809</v>
+        <v>1.043304039395458</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.7451285045540388</v>
+        <v>0.743941718109383</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.175666610858151</v>
+        <v>1.17551322085383</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.351742281727574</v>
+        <v>1.351247789349571</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.226107474161452</v>
+        <v>1.274653393927224</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5606204308942111</v>
+        <v>0.5845778398438242</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8427142898765467</v>
+        <v>0.8907259688668674</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.2380940642466172</v>
+        <v>0.2873416266403339</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.05214072868147213</v>
+        <v>0.02111638109822422</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.168451088514324</v>
+        <v>-0.06910376321975065</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.09804908308812799</v>
+        <v>0.001858952930547275</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.1655817056725155</v>
+        <v>0.2892783267007601</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.2039361251697471</v>
+        <v>0.3526256729475747</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.06286755714776149</v>
+        <v>0.2348663167144238</v>
       </c>
     </row>
     <row r="22">
@@ -4743,46 +4743,46 @@
         <v>2328</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9125547598436512</v>
+        <v>0.8833589654910199</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.09725676277344064</v>
+        <v>-0.09844354921809639</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5388996875230703</v>
+        <v>0.5387462975187489</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6691248311114322</v>
+        <v>0.6686303387334291</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.5174332161600717</v>
+        <v>0.5659791359258435</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.130209936335433</v>
+        <v>-0.1062525273858199</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.1290096426806429</v>
+        <v>-0.08099796369032219</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.5531229600069025</v>
+        <v>-0.5038753976131858</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.043658381134485</v>
+        <v>-0.9704012713547883</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.9915153217942319</v>
+        <v>-0.8921679964996585</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.9814398477520214</v>
+        <v>-0.8815318117333462</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.8181957160152535</v>
+        <v>-0.6944990949870089</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.8947039576448148</v>
+        <v>-0.7460144098669872</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.055566245562616</v>
+        <v>-0.8835674859959539</v>
       </c>
     </row>
     <row r="23">
@@ -4792,101 +4792,101 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2478</v>
+        <v>2489</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3091281284379548</v>
+        <v>0.3276179912600981</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.3571623645620292</v>
+        <v>-0.3547843118820921</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.5553121083603116</v>
+        <v>0.5529731016424577</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.747853242952182</v>
+        <v>0.7448979591836604</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3925570560035396</v>
+        <v>0.3577713325697545</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.06856644162167669</v>
+        <v>0.05194418151710067</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1148698209322845</v>
+        <v>-0.1470830813218313</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.1976520700223361</v>
+        <v>-0.2303558499267453</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5184200941160952</v>
+        <v>-0.566097609232358</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3390512575073146</v>
+        <v>-0.405340963280878</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2794552805048625</v>
+        <v>-0.346417383707994</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2225023339068457</v>
+        <v>-0.3059870495616295</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3780271023004715</v>
+        <v>-0.4779317700292935</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.4120684130904735</v>
+        <v>-0.52779245386143</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 866</t>
+          <t>X &lt; 865.9</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2616</v>
+        <v>2627</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.08660013530816713</v>
+        <v>0.1035245387493759</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.8577033412542008</v>
+        <v>-0.8534253253516653</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2805545133018228</v>
+        <v>-0.279293767197565</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3200908628608232</v>
+        <v>-0.3184625385990643</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7235093464319817</v>
+        <v>-0.7492751543922083</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.091466327249861</v>
+        <v>-1.101120710774907</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.308275009977343</v>
+        <v>-1.33130129287489</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.411738009508731</v>
+        <v>-1.435074440164563</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.833751221017479</v>
+        <v>-1.869590734374036</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.747266744894375</v>
+        <v>-1.798980897399716</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.816682306705822</v>
+        <v>-1.868459019604458</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.914294886705093</v>
+        <v>-1.979825725394093</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.199055494713441</v>
+        <v>-2.278283863334018</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.296541686150277</v>
+        <v>-2.389260415748709</v>
       </c>
     </row>
     <row r="25">
@@ -4896,101 +4896,101 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2757</v>
+        <v>2768</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1343456334224413</v>
+        <v>-0.1188856472530446</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.040458931109917</v>
+        <v>-1.035734953208298</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6212665719370349</v>
+        <v>-0.6187289494550541</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5438547254442909</v>
+        <v>-0.5414481127224136</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9903826033269354</v>
+        <v>-1.01131817742499</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.324507830359281</v>
+        <v>-1.331531551321966</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.317585390762254</v>
+        <v>-1.336965271204015</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.511992185523759</v>
+        <v>-1.531241687932962</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.951816720502087</v>
+        <v>-1.981640603005225</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.985633195815183</v>
+        <v>-2.028717586657507</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.098278335724537</v>
+        <v>-2.14121885016899</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.334227596683213</v>
+        <v>-2.388458676661067</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.807352946278939</v>
+        <v>-2.872559033144597</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.852258077787241</v>
+        <v>-2.929283871590769</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 959.1</t>
+          <t>X &lt; 959</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2898</v>
+        <v>2909</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1964776931932306</v>
+        <v>-0.1829386558246924</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.033682879611924</v>
+        <v>-1.029269738526231</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.7914455262287774</v>
+        <v>-0.7883967613712386</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7459193413810823</v>
+        <v>-0.7428914011647834</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.9905691528106715</v>
+        <v>-1.008146624551259</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.43170015801212</v>
+        <v>-1.436822111774994</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.394838791381481</v>
+        <v>-1.410668604166609</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.499205150231539</v>
+        <v>-1.515189668507297</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.851730490446684</v>
+        <v>-1.876944396497777</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.856246600850511</v>
+        <v>-1.892925355087719</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.904379680088546</v>
+        <v>-1.941135867471431</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.058153056932433</v>
+        <v>-2.104809081635594</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.287144057264427</v>
+        <v>-2.343952554196889</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.249688747394664</v>
+        <v>-2.316922791665412</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3036</v>
+        <v>3047</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1686825113477255</v>
+        <v>-0.1571706484163897</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.7128370317346651</v>
+        <v>-0.7098302634262907</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6962597899416707</v>
+        <v>-0.693697925172458</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4827153378443043</v>
+        <v>-0.4807934950231356</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.7405865221298455</v>
+        <v>-0.756077861969132</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.082452193087491</v>
+        <v>-1.087518099570453</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.9195401035547235</v>
+        <v>-0.9341970806165705</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9087117275702852</v>
+        <v>-0.9238752175187841</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.149160957041531</v>
+        <v>-1.172454569738363</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.027349107288899</v>
+        <v>-1.060863742697464</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.11522469966004</v>
+        <v>-1.148643523749577</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.161442426072746</v>
+        <v>-1.203623262789201</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.365897156757256</v>
+        <v>-1.416726318301123</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.31958020859048</v>
+        <v>-1.379337084169805</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3177</v>
+        <v>3188</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.02692096006126121</v>
+        <v>0.0359675253160745</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1253413835542716</v>
+        <v>-0.1245389100428369</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2208760177635085</v>
+        <v>-0.2200684738498779</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1460187202680814</v>
+        <v>0.1456714017689649</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.06129071133199204</v>
+        <v>-0.07629503218924327</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.3746439510198201</v>
+        <v>-0.3808655531181486</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.1910682173408844</v>
+        <v>-0.2054675763260363</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.2640145846494093</v>
+        <v>-0.2785549406567256</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.370601603426536</v>
+        <v>-0.3923137883189725</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1344343502611594</v>
+        <v>-0.1651571704655055</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1328695306930854</v>
+        <v>-0.1637834408319421</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1437470953960513</v>
+        <v>-0.1821053387254992</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.2945188361372075</v>
+        <v>-0.3402219467285548</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.2084255532801365</v>
+        <v>-0.2617662295661276</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3315</v>
+        <v>3326</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.0431224310041074</v>
+        <v>0.05053507538255531</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.04942102951943639</v>
+        <v>-0.04895098314049307</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.1573485534524437</v>
+        <v>-0.1567901587710878</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1696674247088339</v>
+        <v>0.1692360397396371</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.06896099910696307</v>
+        <v>0.05615672754240109</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1588037317403632</v>
+        <v>-0.1644883029111313</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.07661500607080285</v>
+        <v>-0.0888080230467736</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2562384046779513</v>
+        <v>-0.2681625557754046</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3308069755119902</v>
+        <v>-0.3487160917290453</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.01086191061440189</v>
+        <v>-0.01495057289049129</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1166629047420216</v>
+        <v>-0.1422072877903702</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.1859482187425385</v>
+        <v>-0.21744715208456</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.3177864608884917</v>
+        <v>-0.3553494660613907</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.1353892929417597</v>
+        <v>-0.1796218984869355</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3456</v>
+        <v>3467</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.01622880078514299</v>
+        <v>-0.01011182488698381</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.02635817896150172</v>
+        <v>-0.02602820294309538</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3766917950564164</v>
+        <v>-0.375468531480017</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.02889302719993481</v>
+        <v>-0.0286987961707581</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1186031415257744</v>
+        <v>-0.1283252547115836</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2961782069321615</v>
+        <v>-0.3002251843118202</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2497013338329594</v>
+        <v>-0.2589027527269891</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.29665658278617</v>
+        <v>-0.3059692131345813</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5151502428314885</v>
+        <v>-0.5287730071458725</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.2220935551136662</v>
+        <v>-0.2420834966526257</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.3528316748398836</v>
+        <v>-0.3725297617615695</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5625506557038946</v>
+        <v>-0.5865473693939052</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6773303732943319</v>
+        <v>-0.7061804047064015</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6379450160857161</v>
+        <v>-0.6717891776056959</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3594</v>
+        <v>3605</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3323160859821002</v>
+        <v>-0.3265850144945048</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.4869995168316876</v>
+        <v>-0.4853265102640165</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.7559442434433734</v>
+        <v>-0.7536198187115204</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5830634591044799</v>
+        <v>-0.5812092471843542</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6901086089513129</v>
+        <v>-0.6958662648352316</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.8496460647940438</v>
+        <v>-0.8509383364582561</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.9749707206935199</v>
+        <v>-0.9797775186674258</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.066009557945037</v>
+        <v>-1.070740579507756</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.278677367890062</v>
+        <v>-1.286652425556078</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.168637396104323</v>
+        <v>-1.181179145602854</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.358078168918865</v>
+        <v>-1.370136744643034</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.558709230458568</v>
+        <v>-1.574017442758667</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.51858974785555</v>
+        <v>-1.538079181639127</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.583579715894039</v>
+        <v>-1.606658744318921</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3735</v>
+        <v>3746</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3197634158064986</v>
+        <v>-0.3153791832269732</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.5025638262936738</v>
+        <v>-0.5009525609209646</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.7495537005582378</v>
+        <v>-0.7473409787408229</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6850862819878216</v>
+        <v>-0.6830214513920652</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7549806529032921</v>
+        <v>-0.7585091751919819</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.8706069018509055</v>
+        <v>-0.8708893775177273</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.8607884110405308</v>
+        <v>-0.8639454888317175</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.9927002823502775</v>
+        <v>-0.9956177169443592</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.119415956892063</v>
+        <v>-1.124804541593832</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.9920437906407713</v>
+        <v>-1.000896518836434</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.128508405280449</v>
+        <v>-1.137029497714209</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.320210949580968</v>
+        <v>-1.330989759423851</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.324165240822516</v>
+        <v>-1.337896850527422</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.404901731837619</v>
+        <v>-1.421162684906861</v>
       </c>
     </row>
     <row r="33">
@@ -5312,101 +5312,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3876</v>
+        <v>3884</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1538396612877548</v>
+        <v>-0.1364910909891108</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1826371030220528</v>
+        <v>-0.2175188895089519</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2805447200846345</v>
+        <v>-0.3150114939929693</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.265037453802428</v>
+        <v>-0.2225768581700791</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3775634004860322</v>
+        <v>-0.3896748134043051</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3751128068660421</v>
+        <v>-0.3855283703344341</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3943525374736083</v>
+        <v>-0.4065576083368327</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5125577289908918</v>
+        <v>-0.5242598533062548</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.5336953131966595</v>
+        <v>-0.547199077131765</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.3128211637186382</v>
+        <v>-0.32818046945372</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4515910451857295</v>
+        <v>-0.466554846485721</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.505966540598024</v>
+        <v>-0.5484554065681024</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4732609068571563</v>
+        <v>-0.517472171015477</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.4394299375396855</v>
+        <v>-0.4857330360895631</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 1332</t>
+          <t>X &lt; 1331</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4001</v>
+        <v>4012</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.08928673307545409</v>
+        <v>-0.08775157643977849</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2919526095189369</v>
+        <v>-0.2911020313152051</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2495853727600021</v>
+        <v>-0.2488961501596734</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2803581628202068</v>
+        <v>-0.2795695105491305</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3313468954166581</v>
+        <v>-0.3325894614123612</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2698013539276332</v>
+        <v>-0.2701238922111742</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3160067824217734</v>
+        <v>-0.3172682913179301</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.3702063801728102</v>
+        <v>-0.3713745722893407</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.367589151645376</v>
+        <v>-0.3698287047628028</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2550003984381206</v>
+        <v>-0.2587052837766706</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3708391082853097</v>
+        <v>-0.3742524084646774</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4224229579549359</v>
+        <v>-0.4267506475427609</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.4038411416301457</v>
+        <v>-0.4093294264411256</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3639972993112082</v>
+        <v>-0.3706303523796208</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4095</v>
+        <v>4104</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1196696819462346</v>
+        <v>-0.1175930005002925</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2084887805253786</v>
+        <v>-0.2303151491098916</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1761087738183988</v>
+        <v>-0.1492383199857272</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1788164524627902</v>
+        <v>-0.1519897215084427</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2653082882309263</v>
+        <v>-0.2633625791791516</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1739713949278752</v>
+        <v>-0.1718555065132108</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1479007711386373</v>
+        <v>-0.14630343447066</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1871385508735983</v>
+        <v>-0.2095843799795389</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1615445599962655</v>
+        <v>-0.1845247401630914</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.09537436376994179</v>
+        <v>-0.1186375120204701</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.09120171298172863</v>
+        <v>-0.1143917265380949</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.06752071872028154</v>
+        <v>-0.09128328307485134</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.03450676584928658</v>
+        <v>-0.05866640161287506</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.009694381553678966</v>
+        <v>-0.01516652942353858</v>
       </c>
     </row>
   </sheetData>
